--- a/data/raw/ITUB4.SA.xlsx
+++ b/data/raw/ITUB4.SA.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F252"/>
+  <dimension ref="A1:F251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,5022 +468,5002 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45833</v>
+        <v>45845</v>
       </c>
       <c r="B2" t="n">
-        <v>32.5294303894043</v>
+        <v>33.10898971557617</v>
       </c>
       <c r="C2" t="n">
-        <v>33.02741743515217</v>
+        <v>33.59811059123539</v>
       </c>
       <c r="D2" t="n">
-        <v>32.40493013390986</v>
+        <v>33.03784740218553</v>
       </c>
       <c r="E2" t="n">
-        <v>32.99184793018659</v>
+        <v>33.56253943454007</v>
       </c>
       <c r="F2" t="n">
-        <v>20384627</v>
+        <v>13885121</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45834</v>
+        <v>45846</v>
       </c>
       <c r="B3" t="n">
-        <v>32.28932571411133</v>
+        <v>33.02896118164062</v>
       </c>
       <c r="C3" t="n">
-        <v>32.71617374947062</v>
+        <v>33.18903842397931</v>
       </c>
       <c r="D3" t="n">
-        <v>32.19150608150337</v>
+        <v>32.81552718800289</v>
       </c>
       <c r="E3" t="n">
-        <v>32.57389223570334</v>
+        <v>33.04674676540697</v>
       </c>
       <c r="F3" t="n">
-        <v>23717707</v>
+        <v>21526588</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45835</v>
+        <v>45847</v>
       </c>
       <c r="B4" t="n">
-        <v>32.25375366210938</v>
+        <v>32.34419250488281</v>
       </c>
       <c r="C4" t="n">
-        <v>32.33378504187608</v>
+        <v>32.98449443162429</v>
       </c>
       <c r="D4" t="n">
-        <v>31.9602947874599</v>
+        <v>32.24636830822338</v>
       </c>
       <c r="E4" t="n">
-        <v>32.01364904063771</v>
+        <v>32.97560164049348</v>
       </c>
       <c r="F4" t="n">
-        <v>14240265</v>
+        <v>16093132</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>45838</v>
+        <v>45848</v>
       </c>
       <c r="B5" t="n">
-        <v>32.85845565795898</v>
+        <v>31.34816360473633</v>
       </c>
       <c r="C5" t="n">
-        <v>32.86734803335208</v>
+        <v>31.92621247442432</v>
       </c>
       <c r="D5" t="n">
-        <v>31.94250954595547</v>
+        <v>31.33927081398885</v>
       </c>
       <c r="E5" t="n">
-        <v>32.14704116811104</v>
+        <v>31.92621247442432</v>
       </c>
       <c r="F5" t="n">
-        <v>30712643</v>
+        <v>39571879</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45839</v>
+        <v>45849</v>
       </c>
       <c r="B6" t="n">
-        <v>33.00760650634766</v>
+        <v>31.09026336669922</v>
       </c>
       <c r="C6" t="n">
-        <v>33.06988636790612</v>
+        <v>31.30369734115473</v>
       </c>
       <c r="D6" t="n">
-        <v>32.7495974278763</v>
+        <v>30.88572218332765</v>
       </c>
       <c r="E6" t="n">
-        <v>32.85635691215985</v>
+        <v>31.25923338573503</v>
       </c>
       <c r="F6" t="n">
-        <v>18712010</v>
+        <v>43139284</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45840</v>
+        <v>45852</v>
       </c>
       <c r="B7" t="n">
-        <v>32.74070358276367</v>
+        <v>31.03690147399902</v>
       </c>
       <c r="C7" t="n">
-        <v>33.16775908036912</v>
+        <v>31.15251123314158</v>
       </c>
       <c r="D7" t="n">
-        <v>32.51828095642927</v>
+        <v>30.69006870235145</v>
       </c>
       <c r="E7" t="n">
-        <v>33.0076128318012</v>
+        <v>31.06357984282733</v>
       </c>
       <c r="F7" t="n">
-        <v>20331479</v>
+        <v>26665052</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45841</v>
+        <v>45853</v>
       </c>
       <c r="B8" t="n">
-        <v>33.55032348632812</v>
+        <v>31.14362144470215</v>
       </c>
       <c r="C8" t="n">
-        <v>33.63039660828936</v>
+        <v>31.32148424247049</v>
       </c>
       <c r="D8" t="n">
-        <v>32.77629262930815</v>
+        <v>30.85014887665046</v>
       </c>
       <c r="E8" t="n">
-        <v>32.77629262930815</v>
+        <v>31.03690446488519</v>
       </c>
       <c r="F8" t="n">
-        <v>13945170</v>
+        <v>27356285</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45842</v>
+        <v>45854</v>
       </c>
       <c r="B9" t="n">
-        <v>33.56811904907227</v>
+        <v>31.2948055267334</v>
       </c>
       <c r="C9" t="n">
-        <v>33.79944180575438</v>
+        <v>31.39262972593016</v>
       </c>
       <c r="D9" t="n">
-        <v>33.43466616709478</v>
+        <v>31.01912200608664</v>
       </c>
       <c r="E9" t="n">
-        <v>33.54142917182221</v>
+        <v>31.20587761311869</v>
       </c>
       <c r="F9" t="n">
-        <v>7528785</v>
+        <v>27655294</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45845</v>
+        <v>45855</v>
       </c>
       <c r="B10" t="n">
-        <v>33.12327575683594</v>
+        <v>31.76613807678223</v>
       </c>
       <c r="C10" t="n">
-        <v>33.61260768094667</v>
+        <v>31.87285505772162</v>
       </c>
       <c r="D10" t="n">
-        <v>33.05210274658523</v>
+        <v>31.29480270600477</v>
       </c>
       <c r="E10" t="n">
-        <v>33.57702117582132</v>
+        <v>31.31259178134489</v>
       </c>
       <c r="F10" t="n">
-        <v>13885121</v>
+        <v>25587775</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45846</v>
+        <v>45856</v>
       </c>
       <c r="B11" t="n">
-        <v>33.0432014465332</v>
+        <v>31.18808555603027</v>
       </c>
       <c r="C11" t="n">
-        <v>33.20334770534267</v>
+        <v>31.76613790461416</v>
       </c>
       <c r="D11" t="n">
-        <v>32.82967543193878</v>
+        <v>31.11694323193643</v>
       </c>
       <c r="E11" t="n">
-        <v>33.06099469846153</v>
+        <v>31.49934370660154</v>
       </c>
       <c r="F11" t="n">
-        <v>21526588</v>
+        <v>32227155</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45847</v>
+        <v>45859</v>
       </c>
       <c r="B12" t="n">
-        <v>32.35813903808594</v>
+        <v>31.55270385742188</v>
       </c>
       <c r="C12" t="n">
-        <v>32.99871705742364</v>
+        <v>31.6416352565157</v>
       </c>
       <c r="D12" t="n">
-        <v>32.26027266048764</v>
+        <v>31.13472872763507</v>
       </c>
       <c r="E12" t="n">
-        <v>32.98982043179899</v>
+        <v>31.17029988958451</v>
       </c>
       <c r="F12" t="n">
-        <v>16093132</v>
+        <v>12354541</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45848</v>
+        <v>45860</v>
       </c>
       <c r="B13" t="n">
-        <v>31.36168098449707</v>
+        <v>31.1258373260498</v>
       </c>
       <c r="C13" t="n">
-        <v>31.93997910980942</v>
+        <v>31.78392481680105</v>
       </c>
       <c r="D13" t="n">
-        <v>31.35278435916358</v>
+        <v>31.07247708652437</v>
       </c>
       <c r="E13" t="n">
-        <v>31.93997910980942</v>
+        <v>31.57049084714009</v>
       </c>
       <c r="F13" t="n">
-        <v>39571879</v>
+        <v>23330324</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45849</v>
+        <v>45861</v>
       </c>
       <c r="B14" t="n">
-        <v>31.10366439819336</v>
+        <v>31.47265815734863</v>
       </c>
       <c r="C14" t="n">
-        <v>31.31719037043544</v>
+        <v>31.59716069033879</v>
       </c>
       <c r="D14" t="n">
-        <v>30.89903505015082</v>
+        <v>31.00132639083886</v>
       </c>
       <c r="E14" t="n">
-        <v>31.27270724943776</v>
+        <v>31.09025427567509</v>
       </c>
       <c r="F14" t="n">
-        <v>43139284</v>
+        <v>13271962</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45852</v>
+        <v>45862</v>
       </c>
       <c r="B15" t="n">
-        <v>31.05029296875</v>
+        <v>31.1791934967041</v>
       </c>
       <c r="C15" t="n">
-        <v>31.16595261004604</v>
+        <v>31.36594909027053</v>
       </c>
       <c r="D15" t="n">
-        <v>30.70331054913435</v>
+        <v>30.99243790313767</v>
       </c>
       <c r="E15" t="n">
-        <v>31.07698284849658</v>
+        <v>31.36594909027053</v>
       </c>
       <c r="F15" t="n">
-        <v>26665052</v>
+        <v>11460089</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45853</v>
+        <v>45863</v>
       </c>
       <c r="B16" t="n">
-        <v>31.15705680847168</v>
+        <v>31.31259346008301</v>
       </c>
       <c r="C16" t="n">
-        <v>31.33499633628226</v>
+        <v>31.56159859755122</v>
       </c>
       <c r="D16" t="n">
-        <v>30.86345763630251</v>
+        <v>31.15251623298169</v>
       </c>
       <c r="E16" t="n">
-        <v>31.05029379093086</v>
+        <v>31.15251623298169</v>
       </c>
       <c r="F16" t="n">
-        <v>27356285</v>
+        <v>18518061</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45854</v>
+        <v>45866</v>
       </c>
       <c r="B17" t="n">
-        <v>31.30829238891602</v>
+        <v>30.65449905395508</v>
       </c>
       <c r="C17" t="n">
-        <v>31.40615874659468</v>
+        <v>31.41041416175267</v>
       </c>
       <c r="D17" t="n">
-        <v>31.03249005923414</v>
+        <v>30.36991928977504</v>
       </c>
       <c r="E17" t="n">
-        <v>31.21932615077763</v>
+        <v>31.37483950734263</v>
       </c>
       <c r="F17" t="n">
-        <v>27655294</v>
+        <v>17849385</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45855</v>
+        <v>45867</v>
       </c>
       <c r="B18" t="n">
-        <v>31.77983665466309</v>
+        <v>30.83235740661621</v>
       </c>
       <c r="C18" t="n">
-        <v>31.88659965538842</v>
+        <v>31.00132738164423</v>
       </c>
       <c r="D18" t="n">
-        <v>31.30829802895206</v>
+        <v>30.56556326092243</v>
       </c>
       <c r="E18" t="n">
-        <v>31.32609477551218</v>
+        <v>30.62781627651685</v>
       </c>
       <c r="F18" t="n">
-        <v>25587775</v>
+        <v>16655821</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45856</v>
+        <v>45868</v>
       </c>
       <c r="B19" t="n">
-        <v>31.20152854919434</v>
+        <v>31.18808555603027</v>
       </c>
       <c r="C19" t="n">
-        <v>31.77983005554574</v>
+        <v>31.35705556419362</v>
       </c>
       <c r="D19" t="n">
-        <v>31.13035556064131</v>
+        <v>30.51221251181736</v>
       </c>
       <c r="E19" t="n">
-        <v>31.51292086129286</v>
+        <v>30.6900718162722</v>
       </c>
       <c r="F19" t="n">
-        <v>32227155</v>
+        <v>19531787</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45859</v>
+        <v>45869</v>
       </c>
       <c r="B20" t="n">
-        <v>31.56630706787109</v>
+        <v>31.26812171936035</v>
       </c>
       <c r="C20" t="n">
-        <v>31.65527680765809</v>
+        <v>31.32148195247764</v>
       </c>
       <c r="D20" t="n">
-        <v>31.14815173788089</v>
+        <v>30.80567917781706</v>
       </c>
       <c r="E20" t="n">
-        <v>31.18373823550501</v>
+        <v>30.84125383130191</v>
       </c>
       <c r="F20" t="n">
-        <v>12354541</v>
+        <v>22001830</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45860</v>
+        <v>45870</v>
       </c>
       <c r="B21" t="n">
-        <v>31.13925361633301</v>
+        <v>31.07918548583984</v>
       </c>
       <c r="C21" t="n">
-        <v>31.79762476508565</v>
+        <v>31.81768230084186</v>
       </c>
       <c r="D21" t="n">
-        <v>31.08587037673675</v>
+        <v>30.91013060810221</v>
       </c>
       <c r="E21" t="n">
-        <v>31.58409879815363</v>
+        <v>31.67532269051959</v>
       </c>
       <c r="F21" t="n">
-        <v>23330324</v>
+        <v>16498643</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45861</v>
+        <v>45873</v>
       </c>
       <c r="B22" t="n">
-        <v>31.48624420166016</v>
+        <v>31.40838623046875</v>
       </c>
       <c r="C22" t="n">
-        <v>31.61080047961592</v>
+        <v>31.63972184741166</v>
       </c>
       <c r="D22" t="n">
-        <v>31.01470897174309</v>
+        <v>31.16815335871837</v>
       </c>
       <c r="E22" t="n">
-        <v>31.10367524476305</v>
+        <v>31.53295129374767</v>
       </c>
       <c r="F22" t="n">
-        <v>13271962</v>
+        <v>17430072</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45862</v>
+        <v>45874</v>
       </c>
       <c r="B23" t="n">
-        <v>31.19263076782227</v>
+        <v>31.75539398193359</v>
       </c>
       <c r="C23" t="n">
-        <v>31.3794668472917</v>
+        <v>31.96893509484347</v>
       </c>
       <c r="D23" t="n">
-        <v>31.00579468835283</v>
+        <v>31.19484593856432</v>
       </c>
       <c r="E23" t="n">
-        <v>31.3794668472917</v>
+        <v>31.33720901115388</v>
       </c>
       <c r="F23" t="n">
-        <v>11460089</v>
+        <v>49690805</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45863</v>
+        <v>45875</v>
       </c>
       <c r="B24" t="n">
-        <v>31.32608795166016</v>
+        <v>32.15579605102539</v>
       </c>
       <c r="C24" t="n">
-        <v>31.57520040051203</v>
+        <v>33.05445059825803</v>
       </c>
       <c r="D24" t="n">
-        <v>31.16594173759372</v>
+        <v>32.12020352204169</v>
       </c>
       <c r="E24" t="n">
-        <v>31.16594173759372</v>
+        <v>32.28925842078098</v>
       </c>
       <c r="F24" t="n">
-        <v>18518061</v>
+        <v>41157358</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45866</v>
+        <v>45876</v>
       </c>
       <c r="B25" t="n">
-        <v>30.6677188873291</v>
+        <v>32.72522735595703</v>
       </c>
       <c r="C25" t="n">
-        <v>31.42395998550587</v>
+        <v>32.9298712207737</v>
       </c>
       <c r="D25" t="n">
-        <v>30.38301639737699</v>
+        <v>32.12909027219116</v>
       </c>
       <c r="E25" t="n">
-        <v>31.38836998943252</v>
+        <v>32.24476158358718</v>
       </c>
       <c r="F25" t="n">
-        <v>17849385</v>
+        <v>26887326</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45867</v>
+        <v>45877</v>
       </c>
       <c r="B26" t="n">
-        <v>30.84566497802734</v>
+        <v>32.94766998291016</v>
       </c>
       <c r="C26" t="n">
-        <v>31.0147078822829</v>
+        <v>33.05444405274187</v>
       </c>
       <c r="D26" t="n">
-        <v>30.57875568115978</v>
+        <v>32.69853980923628</v>
       </c>
       <c r="E26" t="n">
-        <v>30.64103556581385</v>
+        <v>32.73412883519682</v>
       </c>
       <c r="F26" t="n">
-        <v>16655821</v>
+        <v>18329262</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45868</v>
+        <v>45880</v>
       </c>
       <c r="B27" t="n">
-        <v>31.20152854919434</v>
+        <v>33.15231323242188</v>
       </c>
       <c r="C27" t="n">
-        <v>31.37057138846047</v>
+        <v>33.25018654789393</v>
       </c>
       <c r="D27" t="n">
-        <v>30.52536418358252</v>
+        <v>32.68964191999034</v>
       </c>
       <c r="E27" t="n">
-        <v>30.70330015069143</v>
+        <v>32.75192621019073</v>
       </c>
       <c r="F27" t="n">
-        <v>19531787</v>
+        <v>22695226</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45869</v>
+        <v>45881</v>
       </c>
       <c r="B28" t="n">
-        <v>31.28160095214844</v>
+        <v>33.83742523193359</v>
       </c>
       <c r="C28" t="n">
-        <v>31.33498418808663</v>
+        <v>34.05096636788508</v>
       </c>
       <c r="D28" t="n">
-        <v>30.81895905834713</v>
+        <v>33.26797987207972</v>
       </c>
       <c r="E28" t="n">
-        <v>30.85454904754802</v>
+        <v>33.33026416005509</v>
       </c>
       <c r="F28" t="n">
-        <v>22001830</v>
+        <v>27812781</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45870</v>
+        <v>45882</v>
       </c>
       <c r="B29" t="n">
-        <v>31.09258651733398</v>
+        <v>33.51711654663086</v>
       </c>
       <c r="C29" t="n">
-        <v>31.83140176471836</v>
+        <v>33.91750708659365</v>
       </c>
       <c r="D29" t="n">
-        <v>30.92345874483719</v>
+        <v>33.49932203302809</v>
       </c>
       <c r="E29" t="n">
-        <v>31.68898077036715</v>
+        <v>33.73955495861571</v>
       </c>
       <c r="F29" t="n">
-        <v>16498643</v>
+        <v>22618491</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45873</v>
+        <v>45883</v>
       </c>
       <c r="B30" t="n">
-        <v>31.42193984985352</v>
+        <v>33.47262954711914</v>
       </c>
       <c r="C30" t="n">
-        <v>31.65337529474935</v>
+        <v>33.81073931755803</v>
       </c>
       <c r="D30" t="n">
-        <v>31.1816033107296</v>
+        <v>33.17011579879296</v>
       </c>
       <c r="E30" t="n">
-        <v>31.5465586665295</v>
+        <v>33.23239660157611</v>
       </c>
       <c r="F30" t="n">
-        <v>17430072</v>
+        <v>26818728</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45874</v>
+        <v>45884</v>
       </c>
       <c r="B31" t="n">
-        <v>31.76909065246582</v>
+        <v>33.35695266723633</v>
       </c>
       <c r="C31" t="n">
-        <v>31.98272386948469</v>
+        <v>33.65946630191131</v>
       </c>
       <c r="D31" t="n">
-        <v>31.20830083467952</v>
+        <v>33.23238411651823</v>
       </c>
       <c r="E31" t="n">
-        <v>31.35072531101367</v>
+        <v>33.35695266723633</v>
       </c>
       <c r="F31" t="n">
-        <v>49690805</v>
+        <v>19527976</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45875</v>
+        <v>45887</v>
       </c>
       <c r="B32" t="n">
-        <v>32.16965484619141</v>
+        <v>33.59719848632812</v>
       </c>
       <c r="C32" t="n">
-        <v>33.06869670367055</v>
+        <v>33.8641232072072</v>
       </c>
       <c r="D32" t="n">
-        <v>32.13404697721837</v>
+        <v>33.37476005360374</v>
       </c>
       <c r="E32" t="n">
-        <v>32.30317473676352</v>
+        <v>33.45483537228216</v>
       </c>
       <c r="F32" t="n">
-        <v>41157358</v>
+        <v>21658634</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45876</v>
+        <v>45888</v>
       </c>
       <c r="B33" t="n">
-        <v>32.73934173583984</v>
+        <v>32.6209831237793</v>
       </c>
       <c r="C33" t="n">
-        <v>32.94407386348865</v>
+        <v>33.16901083388376</v>
       </c>
       <c r="D33" t="n">
-        <v>32.14294753834422</v>
+        <v>32.24365656217135</v>
       </c>
       <c r="E33" t="n">
-        <v>32.25866873873912</v>
+        <v>33.16002359032381</v>
       </c>
       <c r="F33" t="n">
-        <v>26887326</v>
+        <v>40817973</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45877</v>
+        <v>45889</v>
       </c>
       <c r="B34" t="n">
-        <v>32.96187591552734</v>
+        <v>32.63895034790039</v>
       </c>
       <c r="C34" t="n">
-        <v>33.06869602276449</v>
+        <v>32.81863167894591</v>
       </c>
       <c r="D34" t="n">
-        <v>32.71263832526037</v>
+        <v>32.38739930839378</v>
       </c>
       <c r="E34" t="n">
-        <v>32.74824269601783</v>
+        <v>32.58504806655457</v>
       </c>
       <c r="F34" t="n">
-        <v>18329262</v>
+        <v>16894884</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45880</v>
+        <v>45890</v>
       </c>
       <c r="B35" t="n">
-        <v>33.16660690307617</v>
+        <v>32.67489624023438</v>
       </c>
       <c r="C35" t="n">
-        <v>33.26452241677818</v>
+        <v>32.72879853396606</v>
       </c>
       <c r="D35" t="n">
-        <v>32.70373610919927</v>
+        <v>32.33350092681155</v>
       </c>
       <c r="E35" t="n">
-        <v>32.76604725336682</v>
+        <v>32.38740675049044</v>
       </c>
       <c r="F35" t="n">
-        <v>22695226</v>
+        <v>16147619</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45881</v>
+        <v>45891</v>
       </c>
       <c r="B36" t="n">
-        <v>33.85202026367188</v>
+        <v>33.59125518798828</v>
       </c>
       <c r="C36" t="n">
-        <v>34.06565350591205</v>
+        <v>33.61820985815297</v>
       </c>
       <c r="D36" t="n">
-        <v>33.28232928604292</v>
+        <v>32.69285560780558</v>
       </c>
       <c r="E36" t="n">
-        <v>33.34464043898078</v>
+        <v>32.79167998521924</v>
       </c>
       <c r="F36" t="n">
-        <v>27812781</v>
+        <v>32623087</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45882</v>
+        <v>45894</v>
       </c>
       <c r="B37" t="n">
-        <v>33.53156280517578</v>
+        <v>33.42056274414062</v>
       </c>
       <c r="C37" t="n">
-        <v>33.93212591801642</v>
+        <v>33.76195446017315</v>
       </c>
       <c r="D37" t="n">
-        <v>33.51376062193521</v>
+        <v>33.33970578956946</v>
       </c>
       <c r="E37" t="n">
-        <v>33.7540970906468</v>
+        <v>33.6721137917548</v>
       </c>
       <c r="F37" t="n">
-        <v>22618491</v>
+        <v>11064054</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45883</v>
+        <v>45895</v>
       </c>
       <c r="B38" t="n">
-        <v>33.487060546875</v>
+        <v>33.19596862792969</v>
       </c>
       <c r="C38" t="n">
-        <v>33.82531608602345</v>
+        <v>33.50142554184962</v>
       </c>
       <c r="D38" t="n">
-        <v>33.18441637629376</v>
+        <v>32.83660589157817</v>
       </c>
       <c r="E38" t="n">
-        <v>33.24672403009703</v>
+        <v>33.4654871502462</v>
       </c>
       <c r="F38" t="n">
-        <v>26818728</v>
+        <v>22088247</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45884</v>
+        <v>45896</v>
       </c>
       <c r="B39" t="n">
-        <v>33.37134552001953</v>
+        <v>33.75298309326172</v>
       </c>
       <c r="C39" t="n">
-        <v>33.67398968323086</v>
+        <v>33.77095052752863</v>
       </c>
       <c r="D39" t="n">
-        <v>33.24672322048241</v>
+        <v>32.92645287740163</v>
       </c>
       <c r="E39" t="n">
-        <v>33.37134552001953</v>
+        <v>33.06121216435123</v>
       </c>
       <c r="F39" t="n">
-        <v>19527976</v>
+        <v>12612968</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45887</v>
+        <v>45897</v>
       </c>
       <c r="B40" t="n">
-        <v>33.6116828918457</v>
+        <v>34.45373153686523</v>
       </c>
       <c r="C40" t="n">
-        <v>33.87872268916193</v>
+        <v>34.78613960080553</v>
       </c>
       <c r="D40" t="n">
-        <v>33.38914856158796</v>
+        <v>33.88773980960983</v>
       </c>
       <c r="E40" t="n">
-        <v>33.46925840229322</v>
+        <v>33.9955479257512</v>
       </c>
       <c r="F40" t="n">
-        <v>21658634</v>
+        <v>25167947</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45888</v>
+        <v>45898</v>
       </c>
       <c r="B41" t="n">
-        <v>32.63505554199219</v>
+        <v>34.57950210571289</v>
       </c>
       <c r="C41" t="n">
-        <v>33.1833196666492</v>
+        <v>34.72324506322468</v>
       </c>
       <c r="D41" t="n">
-        <v>32.25756620487383</v>
+        <v>34.42677543397829</v>
       </c>
       <c r="E41" t="n">
-        <v>33.17432854606783</v>
+        <v>34.56153467726725</v>
       </c>
       <c r="F41" t="n">
-        <v>40817973</v>
+        <v>32600942</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45889</v>
+        <v>45901</v>
       </c>
       <c r="B42" t="n">
-        <v>32.65303421020508</v>
+        <v>34.85602569580078</v>
       </c>
       <c r="C42" t="n">
-        <v>32.8327930745995</v>
+        <v>35.11668000657392</v>
       </c>
       <c r="D42" t="n">
-        <v>32.40137462522855</v>
+        <v>34.59536785346138</v>
       </c>
       <c r="E42" t="n">
-        <v>32.5991086697685</v>
+        <v>34.68524974628303</v>
       </c>
       <c r="F42" t="n">
-        <v>16894884</v>
+        <v>14863209</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45890</v>
+        <v>45902</v>
       </c>
       <c r="B43" t="n">
-        <v>32.68898773193359</v>
+        <v>34.2628059387207</v>
       </c>
       <c r="C43" t="n">
-        <v>32.74291327175975</v>
+        <v>34.58637862087429</v>
       </c>
       <c r="D43" t="n">
-        <v>32.34744518715647</v>
+        <v>34.11899350338614</v>
       </c>
       <c r="E43" t="n">
-        <v>32.40137425845216</v>
+        <v>34.28976944600864</v>
       </c>
       <c r="F43" t="n">
-        <v>16147619</v>
+        <v>24358676</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45891</v>
+        <v>45903</v>
       </c>
       <c r="B44" t="n">
-        <v>33.60575103759766</v>
+        <v>33.96619415283203</v>
       </c>
       <c r="C44" t="n">
-        <v>33.63271733968389</v>
+        <v>34.41560003268238</v>
       </c>
       <c r="D44" t="n">
-        <v>32.70696376528704</v>
+        <v>33.82238526011835</v>
       </c>
       <c r="E44" t="n">
-        <v>32.80583078901756</v>
+        <v>34.26280330489696</v>
       </c>
       <c r="F44" t="n">
-        <v>32623087</v>
+        <v>20686108</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>45894</v>
+        <v>45904</v>
       </c>
       <c r="B45" t="n">
-        <v>33.43498229980469</v>
+        <v>34.10102462768555</v>
       </c>
       <c r="C45" t="n">
-        <v>33.77652131188637</v>
+        <v>34.4695400936581</v>
       </c>
       <c r="D45" t="n">
-        <v>33.35409045888627</v>
+        <v>33.71453701817224</v>
       </c>
       <c r="E45" t="n">
-        <v>33.68664188102918</v>
+        <v>33.95721569525814</v>
       </c>
       <c r="F45" t="n">
-        <v>11064054</v>
+        <v>15877244</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>45895</v>
+        <v>45905</v>
       </c>
       <c r="B46" t="n">
-        <v>33.21028137207031</v>
+        <v>34.47852325439453</v>
       </c>
       <c r="C46" t="n">
-        <v>33.51586998652003</v>
+        <v>34.89197785205323</v>
       </c>
       <c r="D46" t="n">
-        <v>32.85076369320284</v>
+        <v>34.23584461022663</v>
       </c>
       <c r="E46" t="n">
-        <v>33.47991609975183</v>
+        <v>34.44257190905598</v>
       </c>
       <c r="F46" t="n">
-        <v>22088247</v>
+        <v>15664343</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>45896</v>
+        <v>45908</v>
       </c>
       <c r="B47" t="n">
-        <v>33.76753234863281</v>
+        <v>34.31673049926758</v>
       </c>
       <c r="C47" t="n">
-        <v>33.78550752777929</v>
+        <v>34.52345774888286</v>
       </c>
       <c r="D47" t="n">
-        <v>32.94064585613936</v>
+        <v>33.94821517101186</v>
       </c>
       <c r="E47" t="n">
-        <v>33.07546323120739</v>
+        <v>34.47851504634252</v>
       </c>
       <c r="F47" t="n">
-        <v>12612968</v>
+        <v>11800195</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>45897</v>
+        <v>45909</v>
       </c>
       <c r="B48" t="n">
-        <v>34.46858978271484</v>
+        <v>34.02013397216797</v>
       </c>
       <c r="C48" t="n">
-        <v>34.80114119834786</v>
+        <v>34.48751564961746</v>
       </c>
       <c r="D48" t="n">
-        <v>33.90235397030937</v>
+        <v>33.97519125298749</v>
       </c>
       <c r="E48" t="n">
-        <v>34.01020857893277</v>
+        <v>34.48751564961746</v>
       </c>
       <c r="F48" t="n">
-        <v>25167947</v>
+        <v>19497179</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>45898</v>
+        <v>45910</v>
       </c>
       <c r="B49" t="n">
-        <v>34.59442138671875</v>
+        <v>34.04709625244141</v>
       </c>
       <c r="C49" t="n">
-        <v>34.73822636194176</v>
+        <v>34.4695387269874</v>
       </c>
       <c r="D49" t="n">
-        <v>34.44162882126115</v>
+        <v>33.97519002329528</v>
       </c>
       <c r="E49" t="n">
-        <v>34.57644620624958</v>
+        <v>34.02912057804654</v>
       </c>
       <c r="F49" t="n">
-        <v>32600942</v>
+        <v>14517129</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>45901</v>
+        <v>45911</v>
       </c>
       <c r="B50" t="n">
-        <v>34.87105560302734</v>
+        <v>34.11001586914062</v>
       </c>
       <c r="C50" t="n">
-        <v>35.13182230785663</v>
+        <v>34.82007622263314</v>
       </c>
       <c r="D50" t="n">
-        <v>34.61028536510899</v>
+        <v>34.11001586914062</v>
       </c>
       <c r="E50" t="n">
-        <v>34.70020601497431</v>
+        <v>34.1998942443421</v>
       </c>
       <c r="F50" t="n">
-        <v>14863209</v>
+        <v>18078972</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>45902</v>
+        <v>45912</v>
       </c>
       <c r="B51" t="n">
-        <v>34.277587890625</v>
+        <v>33.59769058227539</v>
       </c>
       <c r="C51" t="n">
-        <v>34.60130017126428</v>
+        <v>33.93923899368995</v>
       </c>
       <c r="D51" t="n">
-        <v>34.13371341050327</v>
+        <v>33.48982947175847</v>
       </c>
       <c r="E51" t="n">
-        <v>34.30456303073917</v>
+        <v>33.90328764456211</v>
       </c>
       <c r="F51" t="n">
-        <v>24358676</v>
+        <v>22589754</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>45903</v>
+        <v>45915</v>
       </c>
       <c r="B52" t="n">
-        <v>33.98085021972656</v>
+        <v>34.15494918823242</v>
       </c>
       <c r="C52" t="n">
-        <v>34.4304500136377</v>
+        <v>34.31673729893024</v>
       </c>
       <c r="D52" t="n">
-        <v>33.83697927494011</v>
+        <v>33.6246492078259</v>
       </c>
       <c r="E52" t="n">
-        <v>34.2775873556202</v>
+        <v>33.71453109915066</v>
       </c>
       <c r="F52" t="n">
-        <v>20686108</v>
+        <v>14196181</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>45904</v>
+        <v>45916</v>
       </c>
       <c r="B53" t="n">
-        <v>34.1157341003418</v>
+        <v>34.06507110595703</v>
       </c>
       <c r="C53" t="n">
-        <v>34.48440852541394</v>
+        <v>34.3796559949865</v>
       </c>
       <c r="D53" t="n">
-        <v>33.72907977944705</v>
+        <v>33.85834379226434</v>
       </c>
       <c r="E53" t="n">
-        <v>33.97186313594958</v>
+        <v>34.32572544153481</v>
       </c>
       <c r="F53" t="n">
-        <v>15877244</v>
+        <v>19993536</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>45905</v>
+        <v>45917</v>
       </c>
       <c r="B54" t="n">
-        <v>34.49338531494141</v>
+        <v>34.55042266845703</v>
       </c>
       <c r="C54" t="n">
-        <v>34.90701813332083</v>
+        <v>34.89197097656999</v>
       </c>
       <c r="D54" t="n">
-        <v>34.25060206348866</v>
+        <v>34.02911060594118</v>
       </c>
       <c r="E54" t="n">
-        <v>34.45741847267838</v>
+        <v>34.09202544788624</v>
       </c>
       <c r="F54" t="n">
-        <v>15664343</v>
+        <v>25226348</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>45908</v>
+        <v>45918</v>
       </c>
       <c r="B55" t="n">
-        <v>34.33154296875</v>
+        <v>34.59536743164062</v>
       </c>
       <c r="C55" t="n">
-        <v>34.53835945009078</v>
+        <v>34.64929797930255</v>
       </c>
       <c r="D55" t="n">
-        <v>33.96286857458171</v>
+        <v>34.29875824841562</v>
       </c>
       <c r="E55" t="n">
-        <v>34.49339734848765</v>
+        <v>34.55042825156087</v>
       </c>
       <c r="F55" t="n">
-        <v>11800195</v>
+        <v>15433005</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>45909</v>
+        <v>45919</v>
       </c>
       <c r="B56" t="n">
-        <v>34.03479766845703</v>
+        <v>35.05376434326172</v>
       </c>
       <c r="C56" t="n">
-        <v>34.50238080140269</v>
+        <v>35.05376434326172</v>
       </c>
       <c r="D56" t="n">
-        <v>33.98983557761901</v>
+        <v>34.559415709955</v>
       </c>
       <c r="E56" t="n">
-        <v>34.50238080140269</v>
+        <v>34.60435488954371</v>
       </c>
       <c r="F56" t="n">
-        <v>19497179</v>
+        <v>26702853</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>45910</v>
+        <v>45922</v>
       </c>
       <c r="B57" t="n">
-        <v>34.0617790222168</v>
+        <v>34.55042266845703</v>
       </c>
       <c r="C57" t="n">
-        <v>34.48440367457764</v>
+        <v>34.92792231482431</v>
       </c>
       <c r="D57" t="n">
-        <v>33.98984178359485</v>
+        <v>34.40661025230847</v>
       </c>
       <c r="E57" t="n">
-        <v>34.04379559583373</v>
+        <v>34.81107693393214</v>
       </c>
       <c r="F57" t="n">
-        <v>14517129</v>
+        <v>18325039</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>45911</v>
+        <v>45923</v>
       </c>
       <c r="B58" t="n">
-        <v>34.12472534179688</v>
+        <v>35.09870147705078</v>
       </c>
       <c r="C58" t="n">
-        <v>34.83509189899783</v>
+        <v>35.26947741266621</v>
       </c>
       <c r="D58" t="n">
-        <v>34.12472534179688</v>
+        <v>34.57738936637658</v>
       </c>
       <c r="E58" t="n">
-        <v>34.21464247580479</v>
+        <v>34.57738936637658</v>
       </c>
       <c r="F58" t="n">
-        <v>18078972</v>
+        <v>16930110</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>45912</v>
+        <v>45924</v>
       </c>
       <c r="B59" t="n">
-        <v>33.61217498779297</v>
+        <v>34.86501312255859</v>
       </c>
       <c r="C59" t="n">
-        <v>33.95387064521191</v>
+        <v>35.17959797795752</v>
       </c>
       <c r="D59" t="n">
-        <v>33.50426737693518</v>
+        <v>34.79310690283231</v>
       </c>
       <c r="E59" t="n">
-        <v>33.91790379698546</v>
+        <v>35.10769175823124</v>
       </c>
       <c r="F59" t="n">
-        <v>22589754</v>
+        <v>18713452</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>45915</v>
+        <v>45925</v>
       </c>
       <c r="B60" t="n">
-        <v>34.16968154907227</v>
+        <v>34.58638000488281</v>
       </c>
       <c r="C60" t="n">
-        <v>34.33153944528823</v>
+        <v>35.07174081331844</v>
       </c>
       <c r="D60" t="n">
-        <v>33.63915282961473</v>
+        <v>34.57739216876051</v>
       </c>
       <c r="E60" t="n">
-        <v>33.72907349050254</v>
+        <v>34.88298919161757</v>
       </c>
       <c r="F60" t="n">
-        <v>14196181</v>
+        <v>15146768</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>45916</v>
+        <v>45926</v>
       </c>
       <c r="B61" t="n">
-        <v>34.07976150512695</v>
+        <v>34.75716018676758</v>
       </c>
       <c r="C61" t="n">
-        <v>34.3944820573869</v>
+        <v>34.92793262545278</v>
       </c>
       <c r="D61" t="n">
-        <v>33.87294504126785</v>
+        <v>34.59537205373245</v>
       </c>
       <c r="E61" t="n">
-        <v>34.34052824664169</v>
+        <v>34.64031477138295</v>
       </c>
       <c r="F61" t="n">
-        <v>19993536</v>
+        <v>12786935</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>45917</v>
+        <v>45929</v>
       </c>
       <c r="B62" t="n">
-        <v>34.56532287597656</v>
+        <v>34.95490264892578</v>
       </c>
       <c r="C62" t="n">
-        <v>34.90701848013617</v>
+        <v>35.37734516039791</v>
       </c>
       <c r="D62" t="n">
-        <v>34.04378599253773</v>
+        <v>34.92793560340959</v>
       </c>
       <c r="E62" t="n">
-        <v>34.10672796712339</v>
+        <v>35.12567510217106</v>
       </c>
       <c r="F62" t="n">
-        <v>25226348</v>
+        <v>19124422</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>45918</v>
+        <v>45930</v>
       </c>
       <c r="B63" t="n">
-        <v>34.61029052734375</v>
+        <v>35.11667633056641</v>
       </c>
       <c r="C63" t="n">
-        <v>34.66424433854596</v>
+        <v>35.50316736977179</v>
       </c>
       <c r="D63" t="n">
-        <v>34.3135533984556</v>
+        <v>34.80209150440446</v>
       </c>
       <c r="E63" t="n">
-        <v>34.56533196224991</v>
+        <v>35.41328548635897</v>
       </c>
       <c r="F63" t="n">
-        <v>15433005</v>
+        <v>33263438</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>45919</v>
+        <v>45931</v>
       </c>
       <c r="B64" t="n">
-        <v>35.06888198852539</v>
+        <v>34.48511505126953</v>
       </c>
       <c r="C64" t="n">
-        <v>35.06888198852539</v>
+        <v>35.43828810992347</v>
       </c>
       <c r="D64" t="n">
-        <v>34.57432015736632</v>
+        <v>34.44015555786429</v>
       </c>
       <c r="E64" t="n">
-        <v>34.61927871788568</v>
+        <v>35.30340609654521</v>
       </c>
       <c r="F64" t="n">
-        <v>26702853</v>
+        <v>25519177</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>45922</v>
+        <v>45932</v>
       </c>
       <c r="B65" t="n">
-        <v>34.56532287597656</v>
+        <v>34.10743713378906</v>
       </c>
       <c r="C65" t="n">
-        <v>34.94298532275655</v>
+        <v>34.79983798234858</v>
       </c>
       <c r="D65" t="n">
-        <v>34.42144843931771</v>
+        <v>34.07146954332545</v>
       </c>
       <c r="E65" t="n">
-        <v>34.82608955115165</v>
+        <v>34.54805424961688</v>
       </c>
       <c r="F65" t="n">
-        <v>18325039</v>
+        <v>17094601</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>45923</v>
+        <v>45933</v>
       </c>
       <c r="B66" t="n">
-        <v>35.11384201049805</v>
+        <v>34.35922622680664</v>
       </c>
       <c r="C66" t="n">
-        <v>35.2846916137609</v>
+        <v>34.35922622680664</v>
       </c>
       <c r="D66" t="n">
-        <v>34.59230502132077</v>
+        <v>33.91860904223938</v>
       </c>
       <c r="E66" t="n">
-        <v>34.59230502132077</v>
+        <v>34.08945865675746</v>
       </c>
       <c r="F66" t="n">
-        <v>16930110</v>
+        <v>17766985</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>45924</v>
+        <v>45936</v>
       </c>
       <c r="B67" t="n">
-        <v>34.88005065917969</v>
+        <v>33.96356582641602</v>
       </c>
       <c r="C67" t="n">
-        <v>35.19477119734078</v>
+        <v>34.39519107751294</v>
       </c>
       <c r="D67" t="n">
-        <v>34.80811342577191</v>
+        <v>33.96356582641602</v>
       </c>
       <c r="E67" t="n">
-        <v>35.122833963933</v>
+        <v>34.35023158600801</v>
       </c>
       <c r="F67" t="n">
-        <v>18713452</v>
+        <v>14832309</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>45925</v>
+        <v>45937</v>
       </c>
       <c r="B68" t="n">
-        <v>34.60129165649414</v>
+        <v>33.42403411865234</v>
       </c>
       <c r="C68" t="n">
-        <v>35.08686172450768</v>
+        <v>33.9275945539893</v>
       </c>
       <c r="D68" t="n">
-        <v>34.59229994533545</v>
+        <v>33.24418908708207</v>
       </c>
       <c r="E68" t="n">
-        <v>34.89802872399748</v>
+        <v>33.91860618888941</v>
       </c>
       <c r="F68" t="n">
-        <v>15146768</v>
+        <v>20705472</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>45926</v>
+        <v>45938</v>
       </c>
       <c r="B69" t="n">
-        <v>34.77215194702148</v>
+        <v>33.48698425292969</v>
       </c>
       <c r="C69" t="n">
-        <v>34.94299804475838</v>
+        <v>33.67582122137011</v>
       </c>
       <c r="D69" t="n">
-        <v>34.61029403012342</v>
+        <v>33.31613461785372</v>
       </c>
       <c r="E69" t="n">
-        <v>34.6552561328573</v>
+        <v>33.49597615303036</v>
       </c>
       <c r="F69" t="n">
-        <v>12786935</v>
+        <v>15395204</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>45929</v>
+        <v>45939</v>
       </c>
       <c r="B70" t="n">
-        <v>34.96997451782227</v>
+        <v>33.43302536010742</v>
       </c>
       <c r="C70" t="n">
-        <v>35.39259917822535</v>
+        <v>33.64883798048706</v>
       </c>
       <c r="D70" t="n">
-        <v>34.94299584464461</v>
+        <v>33.23519653589904</v>
       </c>
       <c r="E70" t="n">
-        <v>35.14082060480219</v>
+        <v>33.64883798048706</v>
       </c>
       <c r="F70" t="n">
-        <v>19124422</v>
+        <v>18067539</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>45930</v>
+        <v>45940</v>
       </c>
       <c r="B71" t="n">
-        <v>35.1318244934082</v>
+        <v>33.39706039428711</v>
       </c>
       <c r="C71" t="n">
-        <v>35.51848225195638</v>
+        <v>33.77473431619003</v>
       </c>
       <c r="D71" t="n">
-        <v>34.81710396584532</v>
+        <v>33.29814596393934</v>
       </c>
       <c r="E71" t="n">
-        <v>35.42856159649708</v>
+        <v>33.60388115472671</v>
       </c>
       <c r="F71" t="n">
-        <v>33263438</v>
+        <v>23250808</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>45931</v>
+        <v>45943</v>
       </c>
       <c r="B72" t="n">
-        <v>34.49999237060547</v>
+        <v>33.53193664550781</v>
       </c>
       <c r="C72" t="n">
-        <v>35.45357664029799</v>
+        <v>33.74774924576388</v>
       </c>
       <c r="D72" t="n">
-        <v>34.45501348110022</v>
+        <v>33.52294474826064</v>
       </c>
       <c r="E72" t="n">
-        <v>35.31863643709544</v>
+        <v>33.52294474826064</v>
       </c>
       <c r="F72" t="n">
-        <v>25519177</v>
+        <v>8194989</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>45932</v>
+        <v>45944</v>
       </c>
       <c r="B73" t="n">
-        <v>34.12215042114258</v>
+        <v>33.67581558227539</v>
       </c>
       <c r="C73" t="n">
-        <v>34.81484995800895</v>
+        <v>34.02651376012897</v>
       </c>
       <c r="D73" t="n">
-        <v>34.08616731495751</v>
+        <v>33.44201915248134</v>
       </c>
       <c r="E73" t="n">
-        <v>34.56295761065469</v>
+        <v>33.44201915248134</v>
       </c>
       <c r="F73" t="n">
-        <v>17094601</v>
+        <v>21154861</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>45933</v>
+        <v>45945</v>
       </c>
       <c r="B74" t="n">
-        <v>34.37403869628906</v>
+        <v>33.67581558227539</v>
       </c>
       <c r="C74" t="n">
-        <v>34.37403869628906</v>
+        <v>33.90062011347447</v>
       </c>
       <c r="D74" t="n">
-        <v>33.93323155899828</v>
+        <v>33.32512093758432</v>
       </c>
       <c r="E74" t="n">
-        <v>34.10415482781475</v>
+        <v>33.55891736737837</v>
       </c>
       <c r="F74" t="n">
-        <v>17766985</v>
+        <v>21972166</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>45936</v>
+        <v>45946</v>
       </c>
       <c r="B75" t="n">
-        <v>33.97820663452148</v>
+        <v>33.59488296508789</v>
       </c>
       <c r="C75" t="n">
-        <v>34.4100179480156</v>
+        <v>33.99054061240086</v>
       </c>
       <c r="D75" t="n">
-        <v>33.97820663452148</v>
+        <v>33.36108654918925</v>
       </c>
       <c r="E75" t="n">
-        <v>34.36503907564557</v>
+        <v>33.55891537284573</v>
       </c>
       <c r="F75" t="n">
-        <v>14832309</v>
+        <v>15847580</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>45937</v>
+        <v>45947</v>
       </c>
       <c r="B76" t="n">
-        <v>33.43844985961914</v>
+        <v>33.71178436279297</v>
       </c>
       <c r="C76" t="n">
-        <v>33.94222747989468</v>
+        <v>33.82867903638923</v>
       </c>
       <c r="D76" t="n">
-        <v>33.25852726112861</v>
+        <v>33.28015559447234</v>
       </c>
       <c r="E76" t="n">
-        <v>33.933235238125</v>
+        <v>33.40604923236209</v>
       </c>
       <c r="F76" t="n">
-        <v>20705472</v>
+        <v>17469315</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>45938</v>
+        <v>45950</v>
       </c>
       <c r="B77" t="n">
-        <v>33.50141525268555</v>
+        <v>34.31425857543945</v>
       </c>
       <c r="C77" t="n">
-        <v>33.69033359919887</v>
+        <v>34.48511170010141</v>
       </c>
       <c r="D77" t="n">
-        <v>33.33049199106193</v>
+        <v>33.79271083680855</v>
       </c>
       <c r="E77" t="n">
-        <v>33.51041102778754</v>
+        <v>33.82867842803751</v>
       </c>
       <c r="F77" t="n">
-        <v>15395204</v>
+        <v>19114019</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>45939</v>
+        <v>45951</v>
       </c>
       <c r="B78" t="n">
-        <v>33.44744110107422</v>
+        <v>33.99053955078125</v>
       </c>
       <c r="C78" t="n">
-        <v>33.66334677611461</v>
+        <v>34.37720528795703</v>
       </c>
       <c r="D78" t="n">
-        <v>33.24952697650623</v>
+        <v>33.96356385744216</v>
       </c>
       <c r="E78" t="n">
-        <v>33.66334677611461</v>
+        <v>34.31425847033695</v>
       </c>
       <c r="F78" t="n">
-        <v>18067539</v>
+        <v>14013871</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>45940</v>
+        <v>45952</v>
       </c>
       <c r="B79" t="n">
-        <v>33.41145324707031</v>
+        <v>34.2692985534668</v>
       </c>
       <c r="C79" t="n">
-        <v>33.78928993195578</v>
+        <v>34.2692985534668</v>
       </c>
       <c r="D79" t="n">
-        <v>33.31249618839487</v>
+        <v>33.93658774028646</v>
       </c>
       <c r="E79" t="n">
-        <v>33.61836313932938</v>
+        <v>34.10743732912925</v>
       </c>
       <c r="F79" t="n">
-        <v>23250808</v>
+        <v>13890374</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>45943</v>
+        <v>45953</v>
       </c>
       <c r="B80" t="n">
-        <v>33.54640197753906</v>
+        <v>34.24232482910156</v>
       </c>
       <c r="C80" t="n">
-        <v>33.76230767712764</v>
+        <v>34.4761212482196</v>
       </c>
       <c r="D80" t="n">
-        <v>33.53740620128005</v>
+        <v>34.06247979908969</v>
       </c>
       <c r="E80" t="n">
-        <v>33.53740620128005</v>
+        <v>34.39519063139802</v>
       </c>
       <c r="F80" t="n">
-        <v>8194989</v>
+        <v>11432588</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>45944</v>
+        <v>45954</v>
       </c>
       <c r="B81" t="n">
-        <v>33.69033813476562</v>
+        <v>34.19736480712891</v>
       </c>
       <c r="C81" t="n">
-        <v>34.04118754971942</v>
+        <v>34.63798552265537</v>
       </c>
       <c r="D81" t="n">
-        <v>33.45644088125388</v>
+        <v>34.15240531226021</v>
       </c>
       <c r="E81" t="n">
-        <v>33.45644088125388</v>
+        <v>34.51209187069772</v>
       </c>
       <c r="F81" t="n">
-        <v>21154861</v>
+        <v>10169911</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>45945</v>
+        <v>45957</v>
       </c>
       <c r="B82" t="n">
-        <v>33.69033813476562</v>
+        <v>34.48511505126953</v>
       </c>
       <c r="C82" t="n">
-        <v>33.91523961196432</v>
+        <v>34.71891148330185</v>
       </c>
       <c r="D82" t="n">
-        <v>33.339492254498</v>
+        <v>34.34123760604768</v>
       </c>
       <c r="E82" t="n">
-        <v>33.57338950800975</v>
+        <v>34.45813935522639</v>
       </c>
       <c r="F82" t="n">
-        <v>21972166</v>
+        <v>11194349</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>45946</v>
+        <v>45958</v>
       </c>
       <c r="B83" t="n">
-        <v>33.60937118530273</v>
+        <v>34.60201263427734</v>
       </c>
       <c r="C83" t="n">
-        <v>34.00519946500427</v>
+        <v>34.60201263427734</v>
       </c>
       <c r="D83" t="n">
-        <v>33.37547394172856</v>
+        <v>34.34123697780996</v>
       </c>
       <c r="E83" t="n">
-        <v>33.57338808157933</v>
+        <v>34.38620000355519</v>
       </c>
       <c r="F83" t="n">
-        <v>15847580</v>
+        <v>10478499</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>45947</v>
+        <v>45959</v>
       </c>
       <c r="B84" t="n">
-        <v>33.7263298034668</v>
+        <v>35.37534332275391</v>
       </c>
       <c r="C84" t="n">
-        <v>33.84327491297359</v>
+        <v>35.52820912702792</v>
       </c>
       <c r="D84" t="n">
-        <v>33.29451480262359</v>
+        <v>34.66495862486312</v>
       </c>
       <c r="E84" t="n">
-        <v>33.42046275915815</v>
+        <v>34.66495862486312</v>
       </c>
       <c r="F84" t="n">
-        <v>17469315</v>
+        <v>27235466</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>45950</v>
+        <v>45960</v>
       </c>
       <c r="B85" t="n">
-        <v>34.32905960083008</v>
+        <v>35.33037948608398</v>
       </c>
       <c r="C85" t="n">
-        <v>34.49998642084613</v>
+        <v>35.68107411123776</v>
       </c>
       <c r="D85" t="n">
-        <v>33.80728689911845</v>
+        <v>35.08759117122078</v>
       </c>
       <c r="E85" t="n">
-        <v>33.84327000451712</v>
+        <v>35.31239568989594</v>
       </c>
       <c r="F85" t="n">
-        <v>19114019</v>
+        <v>18657008</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>45951</v>
+        <v>45961</v>
       </c>
       <c r="B86" t="n">
-        <v>34.00519943237305</v>
+        <v>35.46526718139648</v>
       </c>
       <c r="C86" t="n">
-        <v>34.39203193577253</v>
+        <v>35.63611678873907</v>
       </c>
       <c r="D86" t="n">
-        <v>33.97821210460639</v>
+        <v>35.35735733137876</v>
       </c>
       <c r="E86" t="n">
-        <v>34.32905796963097</v>
+        <v>35.46526718139648</v>
       </c>
       <c r="F86" t="n">
-        <v>14013871</v>
+        <v>16449821</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>45952</v>
+        <v>45964</v>
       </c>
       <c r="B87" t="n">
-        <v>34.28408813476562</v>
+        <v>36.05690383911133</v>
       </c>
       <c r="C87" t="n">
-        <v>34.28408813476562</v>
+        <v>36.10188699795582</v>
       </c>
       <c r="D87" t="n">
-        <v>33.95123373377263</v>
+        <v>35.58010568467365</v>
       </c>
       <c r="E87" t="n">
-        <v>34.12215705607338</v>
+        <v>35.89497365760695</v>
       </c>
       <c r="F87" t="n">
-        <v>13890374</v>
+        <v>17968144</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>45953</v>
+        <v>45965</v>
       </c>
       <c r="B88" t="n">
-        <v>34.2570915222168</v>
+        <v>35.94894409179688</v>
       </c>
       <c r="C88" t="n">
-        <v>34.49098876392762</v>
+        <v>36.13786555562646</v>
       </c>
       <c r="D88" t="n">
-        <v>34.07716893566108</v>
+        <v>35.81400170395175</v>
       </c>
       <c r="E88" t="n">
-        <v>34.41002324650896</v>
+        <v>36.02991093840156</v>
       </c>
       <c r="F88" t="n">
-        <v>11432588</v>
+        <v>20386481</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>45954</v>
+        <v>45966</v>
       </c>
       <c r="B89" t="n">
-        <v>34.21211242675781</v>
+        <v>36.10188293457031</v>
       </c>
       <c r="C89" t="n">
-        <v>34.65292316004587</v>
+        <v>36.12887070599272</v>
       </c>
       <c r="D89" t="n">
-        <v>34.167133543099</v>
+        <v>35.35519298059719</v>
       </c>
       <c r="E89" t="n">
-        <v>34.52697521642852</v>
+        <v>35.94894516035505</v>
       </c>
       <c r="F89" t="n">
-        <v>10169911</v>
+        <v>36312135</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>45957</v>
+        <v>45967</v>
       </c>
       <c r="B90" t="n">
-        <v>34.49999237060547</v>
+        <v>36.10188293457031</v>
       </c>
       <c r="C90" t="n">
-        <v>34.73388966540637</v>
+        <v>36.69563157958405</v>
       </c>
       <c r="D90" t="n">
-        <v>34.35605285481507</v>
+        <v>35.99392831413653</v>
       </c>
       <c r="E90" t="n">
-        <v>34.47300503690232</v>
+        <v>36.0658957045963</v>
       </c>
       <c r="F90" t="n">
-        <v>11194349</v>
+        <v>23226500</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>45958</v>
+        <v>45968</v>
       </c>
       <c r="B91" t="n">
-        <v>34.6169319152832</v>
+        <v>36.13786697387695</v>
       </c>
       <c r="C91" t="n">
-        <v>34.6169319152832</v>
+        <v>36.16485474555632</v>
       </c>
       <c r="D91" t="n">
-        <v>34.35604382069438</v>
+        <v>35.77801587917537</v>
       </c>
       <c r="E91" t="n">
-        <v>34.40102623305805</v>
+        <v>36.10188327830446</v>
       </c>
       <c r="F91" t="n">
-        <v>10478499</v>
+        <v>12706904</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>45959</v>
+        <v>45971</v>
       </c>
       <c r="B92" t="n">
-        <v>35.39060211181641</v>
+        <v>36.38076019287109</v>
       </c>
       <c r="C92" t="n">
-        <v>35.54353385317663</v>
+        <v>36.45273111125151</v>
       </c>
       <c r="D92" t="n">
-        <v>34.6799109968215</v>
+        <v>36.1828428183828</v>
       </c>
       <c r="E92" t="n">
-        <v>34.6799109968215</v>
+        <v>36.2997933515361</v>
       </c>
       <c r="F92" t="n">
-        <v>27235466</v>
+        <v>16552409</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>45960</v>
+        <v>45972</v>
       </c>
       <c r="B93" t="n">
-        <v>35.34561538696289</v>
+        <v>37.08246994018555</v>
       </c>
       <c r="C93" t="n">
-        <v>35.69646124594504</v>
+        <v>37.21741233021462</v>
       </c>
       <c r="D93" t="n">
-        <v>35.10272237187417</v>
+        <v>36.38076314949501</v>
       </c>
       <c r="E93" t="n">
-        <v>35.32762383542831</v>
+        <v>36.52470499795383</v>
       </c>
       <c r="F93" t="n">
-        <v>18657008</v>
+        <v>37289193</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>45961</v>
+        <v>45973</v>
       </c>
       <c r="B94" t="n">
-        <v>35.48056030273438</v>
+        <v>36.23682022094727</v>
       </c>
       <c r="C94" t="n">
-        <v>35.65148358282732</v>
+        <v>37.19941574542178</v>
       </c>
       <c r="D94" t="n">
-        <v>35.37260392047367</v>
+        <v>36.10187784810338</v>
       </c>
       <c r="E94" t="n">
-        <v>35.48056030273438</v>
+        <v>37.08246521765793</v>
       </c>
       <c r="F94" t="n">
-        <v>16449821</v>
+        <v>36789128</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>45964</v>
+        <v>45974</v>
       </c>
       <c r="B95" t="n">
-        <v>36.07244873046875</v>
+        <v>36.38076019287109</v>
       </c>
       <c r="C95" t="n">
-        <v>36.1174512825013</v>
+        <v>36.9295291668193</v>
       </c>
       <c r="D95" t="n">
-        <v>35.59544501829536</v>
+        <v>36.14685912656449</v>
       </c>
       <c r="E95" t="n">
-        <v>35.91044873744949</v>
+        <v>36.39875203878025</v>
       </c>
       <c r="F95" t="n">
-        <v>17968144</v>
+        <v>33686974</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>45965</v>
+        <v>45975</v>
       </c>
       <c r="B96" t="n">
-        <v>35.96444702148438</v>
+        <v>36.52470779418945</v>
       </c>
       <c r="C96" t="n">
-        <v>36.15344995741958</v>
+        <v>36.59667518918442</v>
       </c>
       <c r="D96" t="n">
-        <v>35.82944643993138</v>
+        <v>36.1738526046116</v>
       </c>
       <c r="E96" t="n">
-        <v>36.04544878492352</v>
+        <v>36.36277408596208</v>
       </c>
       <c r="F96" t="n">
-        <v>20386481</v>
+        <v>17006742</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>45966</v>
+        <v>45978</v>
       </c>
       <c r="B97" t="n">
-        <v>36.11745834350586</v>
+        <v>36.25481796264648</v>
       </c>
       <c r="C97" t="n">
-        <v>36.14445775824275</v>
+        <v>36.61466906174923</v>
       </c>
       <c r="D97" t="n">
-        <v>35.37044624563232</v>
+        <v>36.15585926386765</v>
       </c>
       <c r="E97" t="n">
-        <v>35.96445458745858</v>
+        <v>36.52470628697354</v>
       </c>
       <c r="F97" t="n">
-        <v>36312135</v>
+        <v>43985120</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>45967</v>
+        <v>45979</v>
       </c>
       <c r="B98" t="n">
-        <v>36.11745834350586</v>
+        <v>36.07489395141602</v>
       </c>
       <c r="C98" t="n">
-        <v>36.71146314906301</v>
+        <v>36.29979913057362</v>
       </c>
       <c r="D98" t="n">
-        <v>36.00945714828919</v>
+        <v>35.89497192893654</v>
       </c>
       <c r="E98" t="n">
-        <v>36.08145558758756</v>
+        <v>35.93995155087032</v>
       </c>
       <c r="F98" t="n">
-        <v>23226500</v>
+        <v>17147337</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>45968</v>
+        <v>45980</v>
       </c>
       <c r="B99" t="n">
-        <v>36.15345001220703</v>
+        <v>35.84999084472656</v>
       </c>
       <c r="C99" t="n">
-        <v>36.18044942130487</v>
+        <v>36.16485882069843</v>
       </c>
       <c r="D99" t="n">
-        <v>35.79344374582899</v>
+        <v>35.75103213600714</v>
       </c>
       <c r="E99" t="n">
-        <v>36.11745080007658</v>
+        <v>36.02991641235179</v>
       </c>
       <c r="F99" t="n">
-        <v>12706904</v>
+        <v>25766686</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>45971</v>
+        <v>45982</v>
       </c>
       <c r="B100" t="n">
-        <v>36.39645385742188</v>
+        <v>35.95794296264648</v>
       </c>
       <c r="C100" t="n">
-        <v>36.46845582208731</v>
+        <v>36.01192204305537</v>
       </c>
       <c r="D100" t="n">
-        <v>36.19845110679335</v>
+        <v>35.58010353876156</v>
       </c>
       <c r="E100" t="n">
-        <v>36.31545208920682</v>
+        <v>35.84998833657303</v>
       </c>
       <c r="F100" t="n">
-        <v>16552409</v>
+        <v>16502454</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>45972</v>
+        <v>45985</v>
       </c>
       <c r="B101" t="n">
-        <v>37.09846496582031</v>
+        <v>35.82300186157227</v>
       </c>
       <c r="C101" t="n">
-        <v>37.23346556143793</v>
+        <v>36.13786982692255</v>
       </c>
       <c r="D101" t="n">
-        <v>36.39645550332492</v>
+        <v>35.73303908079441</v>
       </c>
       <c r="E101" t="n">
-        <v>36.54045943916788</v>
+        <v>35.91296464235013</v>
       </c>
       <c r="F101" t="n">
-        <v>37289193</v>
+        <v>29014997</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>45973</v>
+        <v>45986</v>
       </c>
       <c r="B102" t="n">
-        <v>36.25245666503906</v>
+        <v>35.90396881103516</v>
       </c>
       <c r="C102" t="n">
-        <v>37.2154675562872</v>
+        <v>36.18284954395224</v>
       </c>
       <c r="D102" t="n">
-        <v>36.11745606360736</v>
+        <v>35.74203509826538</v>
       </c>
       <c r="E102" t="n">
-        <v>37.09846656354387</v>
+        <v>35.9849321326756</v>
       </c>
       <c r="F102" t="n">
-        <v>36789128</v>
+        <v>30345963</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>45974</v>
+        <v>45987</v>
       </c>
       <c r="B103" t="n">
-        <v>36.39645385742188</v>
+        <v>36.74961471557617</v>
       </c>
       <c r="C103" t="n">
-        <v>36.94545955529084</v>
+        <v>36.80359026438173</v>
       </c>
       <c r="D103" t="n">
-        <v>36.16245189259492</v>
+        <v>35.95794505513853</v>
       </c>
       <c r="E103" t="n">
-        <v>36.41445346452109</v>
+        <v>36.07489561229509</v>
       </c>
       <c r="F103" t="n">
-        <v>33686974</v>
+        <v>22251296</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>45975</v>
+        <v>45988</v>
       </c>
       <c r="B104" t="n">
-        <v>36.54046249389648</v>
+        <v>36.6236686706543</v>
       </c>
       <c r="C104" t="n">
-        <v>36.61246093156818</v>
+        <v>36.77660647834495</v>
       </c>
       <c r="D104" t="n">
-        <v>36.18945596517079</v>
+        <v>36.50672163555954</v>
       </c>
       <c r="E104" t="n">
-        <v>36.37845893659708</v>
+        <v>36.5786890417717</v>
       </c>
       <c r="F104" t="n">
-        <v>17006742</v>
+        <v>9469408</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>45978</v>
+        <v>45989</v>
       </c>
       <c r="B105" t="n">
-        <v>36.27045822143555</v>
+        <v>37.46031951904297</v>
       </c>
       <c r="C105" t="n">
-        <v>36.63046455961082</v>
+        <v>37.70321657113161</v>
       </c>
       <c r="D105" t="n">
-        <v>36.17145683206426</v>
+        <v>37.06448466768022</v>
       </c>
       <c r="E105" t="n">
-        <v>36.540462975067</v>
+        <v>37.12745967939509</v>
       </c>
       <c r="F105" t="n">
-        <v>43985120</v>
+        <v>45311657</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>45979</v>
+        <v>45992</v>
       </c>
       <c r="B106" t="n">
-        <v>36.09044647216797</v>
+        <v>37.17019653320312</v>
       </c>
       <c r="C106" t="n">
-        <v>36.31544861190073</v>
+        <v>37.57519891007019</v>
       </c>
       <c r="D106" t="n">
-        <v>35.91044688214271</v>
+        <v>37.03519338341876</v>
       </c>
       <c r="E106" t="n">
-        <v>35.95544589558196</v>
+        <v>37.53919641988095</v>
       </c>
       <c r="F106" t="n">
-        <v>17147337</v>
+        <v>15912985</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>45980</v>
+        <v>45993</v>
       </c>
       <c r="B107" t="n">
-        <v>35.86545562744141</v>
+        <v>37.99819946289062</v>
       </c>
       <c r="C107" t="n">
-        <v>36.18045942952418</v>
+        <v>37.99819946289062</v>
       </c>
       <c r="D107" t="n">
-        <v>35.76645423042857</v>
+        <v>37.2961951312741</v>
       </c>
       <c r="E107" t="n">
-        <v>36.04545881042281</v>
+        <v>37.31419460763092</v>
       </c>
       <c r="F107" t="n">
-        <v>25766686</v>
+        <v>21175667</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>45982</v>
+        <v>45994</v>
       </c>
       <c r="B108" t="n">
-        <v>35.97344970703125</v>
+        <v>37.99819946289062</v>
       </c>
       <c r="C108" t="n">
-        <v>36.02745206574065</v>
+        <v>38.21420025165834</v>
       </c>
       <c r="D108" t="n">
-        <v>35.59544734114014</v>
+        <v>37.72819670880953</v>
       </c>
       <c r="E108" t="n">
-        <v>35.86544852588112</v>
+        <v>38.07020090456083</v>
       </c>
       <c r="F108" t="n">
-        <v>16502454</v>
+        <v>23159653</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>45985</v>
+        <v>45995</v>
       </c>
       <c r="B109" t="n">
-        <v>35.83845138549805</v>
+        <v>38.9342041015625</v>
       </c>
       <c r="C109" t="n">
-        <v>36.15345514516794</v>
+        <v>38.9342041015625</v>
       </c>
       <c r="D109" t="n">
-        <v>35.74844980612538</v>
+        <v>38.11519963650166</v>
       </c>
       <c r="E109" t="n">
-        <v>35.92845296487071</v>
+        <v>38.12419937468977</v>
       </c>
       <c r="F109" t="n">
-        <v>29014997</v>
+        <v>23199514</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>45986</v>
+        <v>45996</v>
       </c>
       <c r="B110" t="n">
-        <v>35.9194450378418</v>
+        <v>37.13419342041016</v>
       </c>
       <c r="C110" t="n">
-        <v>36.19844598090883</v>
+        <v>39.06020461285823</v>
       </c>
       <c r="D110" t="n">
-        <v>35.75744152435222</v>
+        <v>37.03519276247491</v>
       </c>
       <c r="E110" t="n">
-        <v>36.0004432583185</v>
+        <v>38.9792034315943</v>
       </c>
       <c r="F110" t="n">
-        <v>30345963</v>
+        <v>39832160</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>45987</v>
+        <v>45999</v>
       </c>
       <c r="B111" t="n">
-        <v>36.76546096801758</v>
+        <v>37.31419372558594</v>
       </c>
       <c r="C111" t="n">
-        <v>36.81945979081331</v>
+        <v>37.87219516067184</v>
       </c>
       <c r="D111" t="n">
-        <v>35.97344994353063</v>
+        <v>37.09819294192412</v>
       </c>
       <c r="E111" t="n">
-        <v>36.09045092919008</v>
+        <v>37.75519503087526</v>
       </c>
       <c r="F111" t="n">
-        <v>22251296</v>
+        <v>40458400</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>45988</v>
+        <v>46000</v>
       </c>
       <c r="B112" t="n">
-        <v>36.63946151733398</v>
+        <v>37.23320007324219</v>
       </c>
       <c r="C112" t="n">
-        <v>36.7924652748171</v>
+        <v>37.35020376293042</v>
       </c>
       <c r="D112" t="n">
-        <v>36.52246405237619</v>
+        <v>36.65719904580337</v>
       </c>
       <c r="E112" t="n">
-        <v>36.59446249235021</v>
+        <v>37.23320007324219</v>
       </c>
       <c r="F112" t="n">
-        <v>9469408</v>
+        <v>24725047</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>45989</v>
+        <v>46001</v>
       </c>
       <c r="B113" t="n">
-        <v>37.47646713256836</v>
+        <v>37.52622985839844</v>
       </c>
       <c r="C113" t="n">
-        <v>37.71946888765404</v>
+        <v>37.71652233969019</v>
       </c>
       <c r="D113" t="n">
-        <v>37.08046165297067</v>
+        <v>37.00291712326123</v>
       </c>
       <c r="E113" t="n">
-        <v>37.14346381064063</v>
+        <v>37.29787215158042</v>
       </c>
       <c r="F113" t="n">
-        <v>45311657</v>
+        <v>25643189</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>45992</v>
+        <v>46002</v>
       </c>
       <c r="B114" t="n">
-        <v>37.18623352050781</v>
+        <v>37.4976806640625</v>
       </c>
       <c r="C114" t="n">
-        <v>37.59141063462628</v>
+        <v>37.8306971603811</v>
       </c>
       <c r="D114" t="n">
-        <v>37.05117212395584</v>
+        <v>37.31689889176767</v>
       </c>
       <c r="E114" t="n">
-        <v>37.55539261125368</v>
+        <v>37.48816622746614</v>
       </c>
       <c r="F114" t="n">
-        <v>15912985</v>
+        <v>21275268</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>45993</v>
+        <v>46003</v>
       </c>
       <c r="B115" t="n">
-        <v>38.01459121704102</v>
+        <v>37.83069610595703</v>
       </c>
       <c r="C115" t="n">
-        <v>38.01459121704102</v>
+        <v>38.11614041133786</v>
       </c>
       <c r="D115" t="n">
-        <v>37.3122840531172</v>
+        <v>37.44059300093328</v>
       </c>
       <c r="E115" t="n">
-        <v>37.33029129413117</v>
+        <v>37.77360948796998</v>
       </c>
       <c r="F115" t="n">
-        <v>21175667</v>
+        <v>17595593</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>45994</v>
+        <v>46006</v>
       </c>
       <c r="B116" t="n">
-        <v>38.01459121704102</v>
+        <v>38.40158462524414</v>
       </c>
       <c r="C116" t="n">
-        <v>38.23068518474552</v>
+        <v>38.61090970099509</v>
       </c>
       <c r="D116" t="n">
-        <v>37.7444719885262</v>
+        <v>37.96390560112523</v>
       </c>
       <c r="E116" t="n">
-        <v>38.08662371886531</v>
+        <v>38.23031729472724</v>
       </c>
       <c r="F116" t="n">
-        <v>23159653</v>
+        <v>17767809</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>45995</v>
+        <v>46007</v>
       </c>
       <c r="B117" t="n">
-        <v>38.95099639892578</v>
+        <v>37.41204452514648</v>
       </c>
       <c r="C117" t="n">
-        <v>38.95099639892578</v>
+        <v>38.25885923414637</v>
       </c>
       <c r="D117" t="n">
-        <v>38.13163869776223</v>
+        <v>37.41204452514648</v>
       </c>
       <c r="E117" t="n">
-        <v>38.14064231753166</v>
+        <v>38.2112870543067</v>
       </c>
       <c r="F117" t="n">
-        <v>23199514</v>
+        <v>20379168</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>45996</v>
+        <v>46008</v>
       </c>
       <c r="B118" t="n">
-        <v>37.15020751953125</v>
+        <v>37.07902526855469</v>
       </c>
       <c r="C118" t="n">
-        <v>39.07704930317583</v>
+        <v>37.4310743268787</v>
       </c>
       <c r="D118" t="n">
-        <v>37.05116416762036</v>
+        <v>36.86970395448509</v>
       </c>
       <c r="E118" t="n">
-        <v>38.99601319020001</v>
+        <v>37.20272040381965</v>
       </c>
       <c r="F118" t="n">
-        <v>39832160</v>
+        <v>31625017</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>45999</v>
+        <v>46009</v>
       </c>
       <c r="B119" t="n">
-        <v>37.33029174804688</v>
+        <v>37.26932525634766</v>
       </c>
       <c r="C119" t="n">
-        <v>37.88853391511003</v>
+        <v>37.35495892085962</v>
       </c>
       <c r="D119" t="n">
-        <v>37.11419777771479</v>
+        <v>36.93630877300718</v>
       </c>
       <c r="E119" t="n">
-        <v>37.77148330932751</v>
+        <v>36.93630877300718</v>
       </c>
       <c r="F119" t="n">
-        <v>40458400</v>
+        <v>21898830</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>46000</v>
+        <v>46010</v>
       </c>
       <c r="B120" t="n">
-        <v>37.2492561340332</v>
+        <v>37.61185455322266</v>
       </c>
       <c r="C120" t="n">
-        <v>37.3663102791846</v>
+        <v>38.05904799045852</v>
       </c>
       <c r="D120" t="n">
-        <v>36.67300671785814</v>
+        <v>37.28835252006462</v>
       </c>
       <c r="E120" t="n">
-        <v>37.2492561340332</v>
+        <v>37.44059097006938</v>
       </c>
       <c r="F120" t="n">
-        <v>24725047</v>
+        <v>35446214</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>46001</v>
+        <v>46013</v>
       </c>
       <c r="B121" t="n">
-        <v>37.54241180419922</v>
+        <v>37.68798446655273</v>
       </c>
       <c r="C121" t="n">
-        <v>37.7327863428314</v>
+        <v>37.79264702868273</v>
       </c>
       <c r="D121" t="n">
-        <v>37.01887340774861</v>
+        <v>37.38351121867615</v>
       </c>
       <c r="E121" t="n">
-        <v>37.31395562567091</v>
+        <v>37.55477858888258</v>
       </c>
       <c r="F121" t="n">
-        <v>25643189</v>
+        <v>15858704</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>46002</v>
+        <v>46014</v>
       </c>
       <c r="B122" t="n">
-        <v>37.51385498046875</v>
+        <v>38.30643844604492</v>
       </c>
       <c r="C122" t="n">
-        <v>37.84701512071638</v>
+        <v>38.39206837711877</v>
       </c>
       <c r="D122" t="n">
-        <v>37.33299522944207</v>
+        <v>37.81166904076362</v>
       </c>
       <c r="E122" t="n">
-        <v>37.50433643989835</v>
+        <v>37.86875939996155</v>
       </c>
       <c r="F122" t="n">
-        <v>21275268</v>
+        <v>10490138</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>46003</v>
+        <v>46017</v>
       </c>
       <c r="B123" t="n">
-        <v>37.84701538085938</v>
+        <v>38.31880569458008</v>
       </c>
       <c r="C123" t="n">
-        <v>38.13258282021786</v>
+        <v>38.43641086359655</v>
       </c>
       <c r="D123" t="n">
-        <v>37.45674399450679</v>
+        <v>37.93659824148173</v>
       </c>
       <c r="E123" t="n">
-        <v>37.78990413704441</v>
+        <v>38.24040598705117</v>
       </c>
       <c r="F123" t="n">
-        <v>17595593</v>
+        <v>12196300</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>46006</v>
+        <v>46020</v>
       </c>
       <c r="B124" t="n">
-        <v>38.41814804077148</v>
+        <v>38.20120239257812</v>
       </c>
       <c r="C124" t="n">
-        <v>38.6275634028542</v>
+        <v>38.4854092627216</v>
       </c>
       <c r="D124" t="n">
-        <v>37.98028023643387</v>
+        <v>38.08360096780499</v>
       </c>
       <c r="E124" t="n">
-        <v>38.24680683903314</v>
+        <v>38.39720725952127</v>
       </c>
       <c r="F124" t="n">
-        <v>17767809</v>
+        <v>10657000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>46007</v>
+        <v>46021</v>
       </c>
       <c r="B125" t="n">
-        <v>37.42818069458008</v>
+        <v>38.44620895385742</v>
       </c>
       <c r="C125" t="n">
-        <v>38.27536064279094</v>
+        <v>38.87741668618613</v>
       </c>
       <c r="D125" t="n">
-        <v>37.42818069458008</v>
+        <v>38.36780924728949</v>
       </c>
       <c r="E125" t="n">
-        <v>38.22776794461916</v>
+        <v>38.44620895385742</v>
       </c>
       <c r="F125" t="n">
-        <v>20379168</v>
+        <v>13764900</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>46008</v>
+        <v>46024</v>
       </c>
       <c r="B126" t="n">
-        <v>37.09502410888672</v>
+        <v>38.38560104370117</v>
       </c>
       <c r="C126" t="n">
-        <v>37.44722506917235</v>
+        <v>38.99349454866356</v>
       </c>
       <c r="D126" t="n">
-        <v>36.88561247695527</v>
+        <v>38.38560104370117</v>
       </c>
       <c r="E126" t="n">
-        <v>37.2187726160703</v>
+        <v>38.85622863530583</v>
       </c>
       <c r="F126" t="n">
-        <v>31625017</v>
+        <v>18846800</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>46009</v>
+        <v>46027</v>
       </c>
       <c r="B127" t="n">
-        <v>37.28540420532227</v>
+        <v>38.94447326660156</v>
       </c>
       <c r="C127" t="n">
-        <v>37.37107481440762</v>
+        <v>39.35627102490542</v>
       </c>
       <c r="D127" t="n">
-        <v>36.95224405007449</v>
+        <v>38.29735983196993</v>
       </c>
       <c r="E127" t="n">
-        <v>36.95224405007449</v>
+        <v>38.47384565416181</v>
       </c>
       <c r="F127" t="n">
-        <v>21898830</v>
+        <v>24438700</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>46010</v>
+        <v>46028</v>
       </c>
       <c r="B128" t="n">
-        <v>37.62807846069336</v>
+        <v>39.17978286743164</v>
       </c>
       <c r="C128" t="n">
-        <v>38.07546479522273</v>
+        <v>39.68963035223958</v>
       </c>
       <c r="D128" t="n">
-        <v>37.30443688464081</v>
+        <v>39.17978286743164</v>
       </c>
       <c r="E128" t="n">
-        <v>37.45674100283863</v>
+        <v>39.30724567368752</v>
       </c>
       <c r="F128" t="n">
-        <v>35446214</v>
+        <v>21959800</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>46013</v>
+        <v>46029</v>
       </c>
       <c r="B129" t="n">
-        <v>37.70422744750977</v>
+        <v>38.55228042602539</v>
       </c>
       <c r="C129" t="n">
-        <v>37.80893511770345</v>
+        <v>39.19939383894627</v>
       </c>
       <c r="D129" t="n">
-        <v>37.3996229760287</v>
+        <v>38.42481761644859</v>
       </c>
       <c r="E129" t="n">
-        <v>37.57096416001616</v>
+        <v>39.12095777627908</v>
       </c>
       <c r="F129" t="n">
-        <v>15858704</v>
+        <v>20894500</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>46014</v>
+        <v>46030</v>
       </c>
       <c r="B130" t="n">
-        <v>38.32295227050781</v>
+        <v>39.15037536621094</v>
       </c>
       <c r="C130" t="n">
-        <v>38.40861911646354</v>
+        <v>39.30725124992859</v>
       </c>
       <c r="D130" t="n">
-        <v>37.82796957118404</v>
+        <v>38.46404197236517</v>
       </c>
       <c r="E130" t="n">
-        <v>37.88508454191489</v>
+        <v>38.58169795009939</v>
       </c>
       <c r="F130" t="n">
-        <v>10490138</v>
+        <v>17209400</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>46017</v>
+        <v>46031</v>
       </c>
       <c r="B131" t="n">
-        <v>38.33533477783203</v>
+        <v>39.07192611694336</v>
       </c>
       <c r="C131" t="n">
-        <v>38.45299067665582</v>
+        <v>39.50333749812733</v>
       </c>
       <c r="D131" t="n">
-        <v>37.95296245689145</v>
+        <v>38.99349006413776</v>
       </c>
       <c r="E131" t="n">
-        <v>38.2569012520442</v>
+        <v>39.15036590996415</v>
       </c>
       <c r="F131" t="n">
-        <v>12196300</v>
+        <v>17023600</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>46020</v>
+        <v>46034</v>
       </c>
       <c r="B132" t="n">
-        <v>38.21767807006836</v>
+        <v>38.71896362304688</v>
       </c>
       <c r="C132" t="n">
-        <v>38.50200751490686</v>
+        <v>39.13076137270377</v>
       </c>
       <c r="D132" t="n">
-        <v>38.10002592534335</v>
+        <v>38.71896362304688</v>
       </c>
       <c r="E132" t="n">
-        <v>38.41376747133954</v>
+        <v>39.0719315198032</v>
       </c>
       <c r="F132" t="n">
-        <v>10657000</v>
+        <v>10672200</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>46021</v>
+        <v>46035</v>
       </c>
       <c r="B133" t="n">
-        <v>38.46278381347656</v>
+        <v>38.40520858764648</v>
       </c>
       <c r="C133" t="n">
-        <v>38.89417744729789</v>
+        <v>38.79740013104399</v>
       </c>
       <c r="D133" t="n">
-        <v>38.38435030736985</v>
+        <v>38.40520858764648</v>
       </c>
       <c r="E133" t="n">
-        <v>38.46278381347656</v>
+        <v>38.69935411530249</v>
       </c>
       <c r="F133" t="n">
-        <v>13764900</v>
+        <v>17397400</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>46024</v>
+        <v>46036</v>
       </c>
       <c r="B134" t="n">
-        <v>38.40215682983398</v>
+        <v>38.82681274414062</v>
       </c>
       <c r="C134" t="n">
-        <v>39.01031252047502</v>
+        <v>38.88564259704287</v>
       </c>
       <c r="D134" t="n">
-        <v>38.40215682983398</v>
+        <v>38.45423489640689</v>
       </c>
       <c r="E134" t="n">
-        <v>38.87298740405564</v>
+        <v>38.699353673176</v>
       </c>
       <c r="F134" t="n">
-        <v>18846800</v>
+        <v>21222100</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>46027</v>
+        <v>46037</v>
       </c>
       <c r="B135" t="n">
-        <v>38.96126174926758</v>
+        <v>39.16017150878906</v>
       </c>
       <c r="C135" t="n">
-        <v>39.37323702851209</v>
+        <v>39.43470706163667</v>
       </c>
       <c r="D135" t="n">
-        <v>38.3138693520061</v>
+        <v>38.88563969615689</v>
       </c>
       <c r="E135" t="n">
-        <v>38.49043125506179</v>
+        <v>39.02290560247297</v>
       </c>
       <c r="F135" t="n">
-        <v>24438700</v>
+        <v>19093500</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>46028</v>
+        <v>46038</v>
       </c>
       <c r="B136" t="n">
-        <v>39.19667816162109</v>
+        <v>38.83662033081055</v>
       </c>
       <c r="C136" t="n">
-        <v>39.70674550531076</v>
+        <v>39.30724794236184</v>
       </c>
       <c r="D136" t="n">
-        <v>39.19667816162109</v>
+        <v>38.68954756585636</v>
       </c>
       <c r="E136" t="n">
-        <v>39.32419593300062</v>
+        <v>39.18959197452796</v>
       </c>
       <c r="F136" t="n">
-        <v>21959800</v>
+        <v>19742500</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>46029</v>
+        <v>46041</v>
       </c>
       <c r="B137" t="n">
-        <v>38.56890106201172</v>
+        <v>38.77779006958008</v>
       </c>
       <c r="C137" t="n">
-        <v>39.21629345807857</v>
+        <v>39.09154180731957</v>
       </c>
       <c r="D137" t="n">
-        <v>38.44138330074499</v>
+        <v>38.75818011844439</v>
       </c>
       <c r="E137" t="n">
-        <v>39.13782358010315</v>
+        <v>38.94447278412554</v>
       </c>
       <c r="F137" t="n">
-        <v>20894500</v>
+        <v>7190900</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>46030</v>
+        <v>46042</v>
       </c>
       <c r="B138" t="n">
-        <v>39.1672477722168</v>
+        <v>39.14056777954102</v>
       </c>
       <c r="C138" t="n">
-        <v>39.32419126380737</v>
+        <v>39.30725050671096</v>
       </c>
       <c r="D138" t="n">
-        <v>38.48061859332254</v>
+        <v>38.3071653643394</v>
       </c>
       <c r="E138" t="n">
-        <v>38.59832527655847</v>
+        <v>38.58169722060045</v>
       </c>
       <c r="F138" t="n">
-        <v>17209400</v>
+        <v>20693900</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>46031</v>
+        <v>46043</v>
       </c>
       <c r="B139" t="n">
-        <v>39.08877944946289</v>
+        <v>40.85639572143555</v>
       </c>
       <c r="C139" t="n">
-        <v>39.520376916161</v>
+        <v>40.95444547580431</v>
       </c>
       <c r="D139" t="n">
-        <v>39.0103095639541</v>
+        <v>39.45431976601121</v>
       </c>
       <c r="E139" t="n">
-        <v>39.16725307680018</v>
+        <v>39.48373282221399</v>
       </c>
       <c r="F139" t="n">
-        <v>17023600</v>
+        <v>39510800</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>46034</v>
+        <v>46044</v>
       </c>
       <c r="B140" t="n">
-        <v>38.73565673828125</v>
+        <v>42.23887252807617</v>
       </c>
       <c r="C140" t="n">
-        <v>39.14763202851891</v>
+        <v>42.71930327150922</v>
       </c>
       <c r="D140" t="n">
-        <v>38.73565673828125</v>
+        <v>41.08191151705129</v>
       </c>
       <c r="E140" t="n">
-        <v>39.08877681198714</v>
+        <v>41.14073763408293</v>
       </c>
       <c r="F140" t="n">
-        <v>10672200</v>
+        <v>42959700</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>46035</v>
+        <v>46045</v>
       </c>
       <c r="B141" t="n">
-        <v>38.42176818847656</v>
+        <v>42.71930313110352</v>
       </c>
       <c r="C141" t="n">
-        <v>38.81412883746278</v>
+        <v>43.0526648406458</v>
       </c>
       <c r="D141" t="n">
-        <v>38.42176818847656</v>
+        <v>42.19965248454665</v>
       </c>
       <c r="E141" t="n">
-        <v>38.71604054613046</v>
+        <v>42.34672151685838</v>
       </c>
       <c r="F141" t="n">
-        <v>17397400</v>
+        <v>41025100</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>46036</v>
+        <v>46048</v>
       </c>
       <c r="B142" t="n">
-        <v>38.84354782104492</v>
+        <v>43.2879753112793</v>
       </c>
       <c r="C142" t="n">
-        <v>38.90240303070563</v>
+        <v>43.47426422584105</v>
       </c>
       <c r="D142" t="n">
-        <v>38.47080938534391</v>
+        <v>42.43495931777558</v>
       </c>
       <c r="E142" t="n">
-        <v>38.71603381285512</v>
+        <v>42.66046813231313</v>
       </c>
       <c r="F142" t="n">
-        <v>21222100</v>
+        <v>25371700</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
-        <v>46037</v>
+        <v>46049</v>
       </c>
       <c r="B143" t="n">
-        <v>39.17705917358398</v>
+        <v>44.43512725830078</v>
       </c>
       <c r="C143" t="n">
-        <v>39.4517131187729</v>
+        <v>45.17048351752714</v>
       </c>
       <c r="D143" t="n">
-        <v>38.90240897022345</v>
+        <v>43.81742695329034</v>
       </c>
       <c r="E143" t="n">
-        <v>39.03973407190372</v>
+        <v>43.90566985400612</v>
       </c>
       <c r="F143" t="n">
-        <v>19093500</v>
+        <v>40280000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>46038</v>
+        <v>46050</v>
       </c>
       <c r="B144" t="n">
-        <v>38.85336303710938</v>
+        <v>45.43521881103516</v>
       </c>
       <c r="C144" t="n">
-        <v>39.32419353912357</v>
+        <v>45.51365487848617</v>
       </c>
       <c r="D144" t="n">
-        <v>38.7062268681801</v>
+        <v>44.73908234896292</v>
       </c>
       <c r="E144" t="n">
-        <v>39.20648684907707</v>
+        <v>44.74888545481333</v>
       </c>
       <c r="F144" t="n">
-        <v>19742500</v>
+        <v>36337500</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>46041</v>
+        <v>46051</v>
       </c>
       <c r="B145" t="n">
-        <v>38.79450607299805</v>
+        <v>45.24892425537109</v>
       </c>
       <c r="C145" t="n">
-        <v>39.10839306019634</v>
+        <v>46.13134954067534</v>
       </c>
       <c r="D145" t="n">
-        <v>38.77488766856965</v>
+        <v>44.75868673901915</v>
       </c>
       <c r="E145" t="n">
-        <v>38.96126063972542</v>
+        <v>45.76857482583522</v>
       </c>
       <c r="F145" t="n">
-        <v>7190900</v>
+        <v>36252700</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>46042</v>
+        <v>46052</v>
       </c>
       <c r="B146" t="n">
-        <v>39.15744781494141</v>
+        <v>44.61161804199219</v>
       </c>
       <c r="C146" t="n">
-        <v>39.32420242687171</v>
+        <v>45.47443719643839</v>
       </c>
       <c r="D146" t="n">
-        <v>38.32368598077708</v>
+        <v>44.10177052982925</v>
       </c>
       <c r="E146" t="n">
-        <v>38.59833623356927</v>
+        <v>45.19009851346402</v>
       </c>
       <c r="F146" t="n">
-        <v>20693900</v>
+        <v>38117000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>46043</v>
+        <v>46055</v>
       </c>
       <c r="B147" t="n">
-        <v>40.87400817871094</v>
+        <v>45.00217819213867</v>
       </c>
       <c r="C147" t="n">
-        <v>40.97210020056511</v>
+        <v>45.21796638386486</v>
       </c>
       <c r="D147" t="n">
-        <v>39.4713278135626</v>
+        <v>44.56078730179554</v>
       </c>
       <c r="E147" t="n">
-        <v>39.50075354920484</v>
+        <v>44.91390001407004</v>
       </c>
       <c r="F147" t="n">
-        <v>39510800</v>
+        <v>28095400</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
-        <v>46044</v>
+        <v>46056</v>
       </c>
       <c r="B148" t="n">
-        <v>42.25708389282227</v>
+        <v>45.2572021484375</v>
       </c>
       <c r="C148" t="n">
-        <v>42.73772177482176</v>
+        <v>46.08113056658389</v>
       </c>
       <c r="D148" t="n">
-        <v>41.09962405600712</v>
+        <v>45.01198540186667</v>
       </c>
       <c r="E148" t="n">
-        <v>41.15847553602337</v>
+        <v>45.4141407165744</v>
       </c>
       <c r="F148" t="n">
-        <v>42959700</v>
+        <v>48570600</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
-        <v>46045</v>
+        <v>46057</v>
       </c>
       <c r="B149" t="n">
-        <v>42.73772430419922</v>
+        <v>43.76628875732422</v>
       </c>
       <c r="C149" t="n">
-        <v>43.07122976406759</v>
+        <v>45.10026860599361</v>
       </c>
       <c r="D149" t="n">
-        <v>42.21784957686837</v>
+        <v>43.20719481217765</v>
       </c>
       <c r="E149" t="n">
-        <v>42.36498202744544</v>
+        <v>45.02180118403653</v>
       </c>
       <c r="F149" t="n">
-        <v>41025100</v>
+        <v>48683500</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
-        <v>46048</v>
+        <v>46058</v>
       </c>
       <c r="B150" t="n">
-        <v>43.30664443969727</v>
+        <v>44.64906311035156</v>
       </c>
       <c r="C150" t="n">
-        <v>43.49301369647053</v>
+        <v>45.00217580388649</v>
       </c>
       <c r="D150" t="n">
-        <v>42.4532605596151</v>
+        <v>43.88398810216616</v>
       </c>
       <c r="E150" t="n">
-        <v>42.67886663102335</v>
+        <v>44.37442156725124</v>
       </c>
       <c r="F150" t="n">
-        <v>25371700</v>
+        <v>36014400</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
-        <v>46049</v>
+        <v>46059</v>
       </c>
       <c r="B151" t="n">
-        <v>44.45429611206055</v>
+        <v>45.85553359985352</v>
       </c>
       <c r="C151" t="n">
-        <v>45.1899695963623</v>
+        <v>46.04189698832367</v>
       </c>
       <c r="D151" t="n">
-        <v>43.83632933753501</v>
+        <v>44.24691227117409</v>
       </c>
       <c r="E151" t="n">
-        <v>43.92461030532437</v>
+        <v>44.71772799602826</v>
       </c>
       <c r="F151" t="n">
-        <v>40280000</v>
+        <v>38175900</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
-        <v>46050</v>
+        <v>46062</v>
       </c>
       <c r="B152" t="n">
-        <v>45.45481109619141</v>
+        <v>47.38568496704102</v>
       </c>
       <c r="C152" t="n">
-        <v>45.53328098634297</v>
+        <v>47.47396314456707</v>
       </c>
       <c r="D152" t="n">
-        <v>44.75837445059569</v>
+        <v>45.84572411375026</v>
       </c>
       <c r="E152" t="n">
-        <v>44.76818178367886</v>
+        <v>46.10074788120855</v>
       </c>
       <c r="F152" t="n">
-        <v>36337500</v>
+        <v>41656900</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
-        <v>46051</v>
+        <v>46063</v>
       </c>
       <c r="B153" t="n">
-        <v>45.26844024658203</v>
+        <v>47.49357223510742</v>
       </c>
       <c r="C153" t="n">
-        <v>46.15124612445054</v>
+        <v>48.24884017696619</v>
       </c>
       <c r="D153" t="n">
-        <v>44.77799128937888</v>
+        <v>47.26797330313042</v>
       </c>
       <c r="E153" t="n">
-        <v>45.78831494383222</v>
+        <v>47.38568002202204</v>
       </c>
       <c r="F153" t="n">
-        <v>36252700</v>
+        <v>43939300</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
-        <v>46052</v>
+        <v>46064</v>
       </c>
       <c r="B154" t="n">
-        <v>44.63085174560547</v>
+        <v>48.4254035949707</v>
       </c>
       <c r="C154" t="n">
-        <v>45.49404289301262</v>
+        <v>48.71966295180974</v>
       </c>
       <c r="D154" t="n">
-        <v>44.12078441949344</v>
+        <v>47.67013554266705</v>
       </c>
       <c r="E154" t="n">
-        <v>45.20958162121062</v>
+        <v>47.86630969446332</v>
       </c>
       <c r="F154" t="n">
-        <v>38117000</v>
+        <v>45819200</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
-        <v>46055</v>
+        <v>46065</v>
       </c>
       <c r="B155" t="n">
-        <v>45.02158737182617</v>
+        <v>47.31703186035156</v>
       </c>
       <c r="C155" t="n">
-        <v>45.23746863175385</v>
+        <v>48.16057444666824</v>
       </c>
       <c r="D155" t="n">
-        <v>44.58000611213988</v>
+        <v>46.95410832927187</v>
       </c>
       <c r="E155" t="n">
-        <v>44.93327111988891</v>
+        <v>48.11153183865267</v>
       </c>
       <c r="F155" t="n">
-        <v>28095400</v>
+        <v>42023800</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
-        <v>46056</v>
+        <v>46066</v>
       </c>
       <c r="B156" t="n">
-        <v>45.2767219543457</v>
+        <v>46.85601806640625</v>
       </c>
       <c r="C156" t="n">
-        <v>46.101005739639</v>
+        <v>47.15027742451628</v>
       </c>
       <c r="D156" t="n">
-        <v>45.03139944376228</v>
+        <v>45.70840170555319</v>
       </c>
       <c r="E156" t="n">
-        <v>45.43372821138612</v>
+        <v>47.15027742451628</v>
       </c>
       <c r="F156" t="n">
-        <v>48570600</v>
+        <v>32353500</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
-        <v>46057</v>
+        <v>46071</v>
       </c>
       <c r="B157" t="n">
-        <v>43.78515625</v>
+        <v>47.07180786132812</v>
       </c>
       <c r="C157" t="n">
-        <v>45.11971117267586</v>
+        <v>47.49357721896356</v>
       </c>
       <c r="D157" t="n">
-        <v>43.22582128142616</v>
+        <v>46.61079918490097</v>
       </c>
       <c r="E157" t="n">
-        <v>45.04120992369002</v>
+        <v>47.15027527377987</v>
       </c>
       <c r="F157" t="n">
-        <v>48683500</v>
+        <v>23368500</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
-        <v>46058</v>
+        <v>46072</v>
       </c>
       <c r="B158" t="n">
-        <v>44.66831970214844</v>
+        <v>47.62109375</v>
       </c>
       <c r="C158" t="n">
-        <v>45.02158468884528</v>
+        <v>48.22923026337087</v>
       </c>
       <c r="D158" t="n">
-        <v>43.90291472652138</v>
+        <v>47.01295723662913</v>
       </c>
       <c r="E158" t="n">
-        <v>44.3935597095283</v>
+        <v>47.1797028363797</v>
       </c>
       <c r="F158" t="n">
-        <v>36014400</v>
+        <v>32026400</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
-        <v>46059</v>
+        <v>46073</v>
       </c>
       <c r="B159" t="n">
-        <v>45.87530517578125</v>
+        <v>48.28808212280273</v>
       </c>
       <c r="C159" t="n">
-        <v>46.06174891873856</v>
+        <v>48.34693549001578</v>
       </c>
       <c r="D159" t="n">
-        <v>44.2659902562472</v>
+        <v>47.1012339468363</v>
       </c>
       <c r="E159" t="n">
-        <v>44.73700898318467</v>
+        <v>47.13065875958748</v>
       </c>
       <c r="F159" t="n">
-        <v>38175900</v>
+        <v>31655900</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
-        <v>46062</v>
+        <v>46076</v>
       </c>
       <c r="B160" t="n">
-        <v>47.40612030029297</v>
+        <v>46.54213714599609</v>
       </c>
       <c r="C160" t="n">
-        <v>47.49443654826114</v>
+        <v>47.95458419545287</v>
       </c>
       <c r="D160" t="n">
-        <v>45.8654953305448</v>
+        <v>46.38519858494534</v>
       </c>
       <c r="E160" t="n">
-        <v>46.12062907838385</v>
+        <v>47.86630602100492</v>
       </c>
       <c r="F160" t="n">
-        <v>41656900</v>
+        <v>34148200</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
-        <v>46063</v>
+        <v>46077</v>
       </c>
       <c r="B161" t="n">
-        <v>47.51406478881836</v>
+        <v>47.24835968017578</v>
       </c>
       <c r="C161" t="n">
-        <v>48.26965861412064</v>
+        <v>47.42491603236119</v>
       </c>
       <c r="D161" t="n">
-        <v>47.28836851528516</v>
+        <v>46.34596387274861</v>
       </c>
       <c r="E161" t="n">
-        <v>47.40612602233917</v>
+        <v>46.72850138858015</v>
       </c>
       <c r="F161" t="n">
-        <v>43939300</v>
+        <v>38465900</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
-        <v>46064</v>
+        <v>46078</v>
       </c>
       <c r="B162" t="n">
-        <v>48.4462890625</v>
+        <v>46.87564086914062</v>
       </c>
       <c r="C162" t="n">
-        <v>48.74067533091408</v>
+        <v>47.57205563088099</v>
       </c>
       <c r="D162" t="n">
-        <v>47.69069526946501</v>
+        <v>46.16941534077792</v>
       </c>
       <c r="E162" t="n">
-        <v>47.8869540295159</v>
+        <v>47.41511704032385</v>
       </c>
       <c r="F162" t="n">
-        <v>45819200</v>
+        <v>28980200</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
-        <v>46065</v>
+        <v>46079</v>
       </c>
       <c r="B163" t="n">
-        <v>47.33742523193359</v>
+        <v>46.7579345703125</v>
       </c>
       <c r="C163" t="n">
-        <v>48.18133138030671</v>
+        <v>47.22875408823</v>
       </c>
       <c r="D163" t="n">
-        <v>46.97434528287639</v>
+        <v>46.25769397737802</v>
       </c>
       <c r="E163" t="n">
-        <v>48.13226763520606</v>
+        <v>46.87564132064747</v>
       </c>
       <c r="F163" t="n">
-        <v>42023800</v>
+        <v>26516600</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
-        <v>46066</v>
+        <v>46080</v>
       </c>
       <c r="B164" t="n">
-        <v>46.87622451782227</v>
+        <v>45.88495635986328</v>
       </c>
       <c r="C164" t="n">
-        <v>47.17061077398442</v>
+        <v>46.70888477691214</v>
       </c>
       <c r="D164" t="n">
-        <v>45.72811325246821</v>
+        <v>45.39452286737492</v>
       </c>
       <c r="E164" t="n">
-        <v>47.17061077398442</v>
+        <v>46.68926698820734</v>
       </c>
       <c r="F164" t="n">
-        <v>32353500</v>
+        <v>44765800</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
-        <v>46071</v>
+        <v>46083</v>
       </c>
       <c r="B165" t="n">
-        <v>47.09210968017578</v>
+        <v>45.05892944335938</v>
       </c>
       <c r="C165" t="n">
-        <v>47.51406094467826</v>
+        <v>45.46124492287085</v>
       </c>
       <c r="D165" t="n">
-        <v>46.63090217317335</v>
+        <v>44.72530854590963</v>
       </c>
       <c r="E165" t="n">
-        <v>47.17061093520263</v>
+        <v>44.97062067156337</v>
       </c>
       <c r="F165" t="n">
-        <v>23368500</v>
+        <v>47144000</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
-        <v>46072</v>
+        <v>46084</v>
       </c>
       <c r="B166" t="n">
-        <v>47.64162445068359</v>
+        <v>43.54780197143555</v>
       </c>
       <c r="C166" t="n">
-        <v>48.25002314763211</v>
+        <v>44.02861155738196</v>
       </c>
       <c r="D166" t="n">
-        <v>47.03322575373508</v>
+        <v>42.62542614480594</v>
       </c>
       <c r="E166" t="n">
-        <v>47.20004324188066</v>
+        <v>43.39080238822534</v>
       </c>
       <c r="F166" t="n">
-        <v>32026400</v>
+        <v>54352300</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
-        <v>46073</v>
+        <v>46085</v>
       </c>
       <c r="B167" t="n">
-        <v>48.30891036987305</v>
+        <v>44.16599273681641</v>
       </c>
       <c r="C167" t="n">
-        <v>48.3677891224901</v>
+        <v>44.63699530439114</v>
       </c>
       <c r="D167" t="n">
-        <v>47.1215502670303</v>
+        <v>43.68518307453417</v>
       </c>
       <c r="E167" t="n">
-        <v>47.15098777167653</v>
+        <v>44.39168318273035</v>
       </c>
       <c r="F167" t="n">
-        <v>31655900</v>
+        <v>27146100</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="B168" t="n">
-        <v>46.56221389770508</v>
+        <v>42.69411468505859</v>
       </c>
       <c r="C168" t="n">
-        <v>47.97527023050063</v>
+        <v>44.15617639490491</v>
       </c>
       <c r="D168" t="n">
-        <v>46.40520763850557</v>
+        <v>42.51749342319119</v>
       </c>
       <c r="E168" t="n">
-        <v>47.88695397574313</v>
+        <v>43.95992597340557</v>
       </c>
       <c r="F168" t="n">
-        <v>34148200</v>
+        <v>37085400</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
-        <v>46077</v>
+        <v>46087</v>
       </c>
       <c r="B169" t="n">
-        <v>47.26873779296875</v>
+        <v>42.12499237060547</v>
       </c>
       <c r="C169" t="n">
-        <v>47.44537029351748</v>
+        <v>42.7726161381153</v>
       </c>
       <c r="D169" t="n">
-        <v>46.3659527842302</v>
+        <v>41.85024402777265</v>
       </c>
       <c r="E169" t="n">
-        <v>46.74865528764433</v>
+        <v>42.64505280330058</v>
       </c>
       <c r="F169" t="n">
-        <v>38465900</v>
+        <v>26063600</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
-        <v>46078</v>
+        <v>46090</v>
       </c>
       <c r="B170" t="n">
-        <v>46.89585113525391</v>
+        <v>42.35068511962891</v>
       </c>
       <c r="C170" t="n">
-        <v>47.59256615374595</v>
+        <v>42.46843389156844</v>
       </c>
       <c r="D170" t="n">
-        <v>46.18932112026233</v>
+        <v>41.55587248691358</v>
       </c>
       <c r="E170" t="n">
-        <v>47.43555989967275</v>
+        <v>41.72268667839673</v>
       </c>
       <c r="F170" t="n">
-        <v>28980200</v>
+        <v>40970400</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
-        <v>46079</v>
+        <v>46091</v>
       </c>
       <c r="B171" t="n">
-        <v>46.77809524536133</v>
+        <v>42.97867584228516</v>
       </c>
       <c r="C171" t="n">
-        <v>47.24911776709828</v>
+        <v>43.3711766691487</v>
       </c>
       <c r="D171" t="n">
-        <v>46.27763896308699</v>
+        <v>42.0170529339513</v>
       </c>
       <c r="E171" t="n">
-        <v>46.89585274745782</v>
+        <v>42.76280375635897</v>
       </c>
       <c r="F171" t="n">
-        <v>26516600</v>
+        <v>50383100</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
-        <v>46080</v>
+        <v>46092</v>
       </c>
       <c r="B172" t="n">
-        <v>45.90474700927734</v>
+        <v>43.06699371337891</v>
       </c>
       <c r="C172" t="n">
-        <v>46.72903079505134</v>
+        <v>43.60667961026311</v>
       </c>
       <c r="D172" t="n">
-        <v>45.41410198782436</v>
+        <v>42.38993363290589</v>
       </c>
       <c r="E172" t="n">
-        <v>46.70940454499429</v>
+        <v>42.4586207247003</v>
       </c>
       <c r="F172" t="n">
-        <v>44765800</v>
+        <v>18482600</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
-        <v>46083</v>
+        <v>46093</v>
       </c>
       <c r="B173" t="n">
-        <v>45.0783576965332</v>
+        <v>41.88949203491211</v>
       </c>
       <c r="C173" t="n">
-        <v>45.48084664414719</v>
+        <v>42.40955622216439</v>
       </c>
       <c r="D173" t="n">
-        <v>44.74459295032052</v>
+        <v>41.50680576525087</v>
       </c>
       <c r="E173" t="n">
-        <v>44.99001084826274</v>
+        <v>42.28199288455547</v>
       </c>
       <c r="F173" t="n">
-        <v>47144000</v>
+        <v>27095200</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
-        <v>46084</v>
+        <v>46094</v>
       </c>
       <c r="B174" t="n">
-        <v>43.56658554077148</v>
+        <v>41.60493469238281</v>
       </c>
       <c r="C174" t="n">
-        <v>44.04760251537556</v>
+        <v>42.53711770104274</v>
       </c>
       <c r="D174" t="n">
-        <v>42.6438118637451</v>
+        <v>41.53624760212715</v>
       </c>
       <c r="E174" t="n">
-        <v>43.40951823858527</v>
+        <v>42.02687181433371</v>
       </c>
       <c r="F174" t="n">
-        <v>54352300</v>
+        <v>24896600</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n">
-        <v>46085</v>
+        <v>46097</v>
       </c>
       <c r="B175" t="n">
-        <v>44.18503189086914</v>
+        <v>42.19368362426758</v>
       </c>
       <c r="C175" t="n">
-        <v>44.6562374990615</v>
+        <v>42.65487159657845</v>
       </c>
       <c r="D175" t="n">
-        <v>43.70401496030959</v>
+        <v>42.04649485854451</v>
       </c>
       <c r="E175" t="n">
-        <v>44.4108196278186</v>
+        <v>42.43899573836216</v>
       </c>
       <c r="F175" t="n">
-        <v>27146100</v>
+        <v>17777300</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
-        <v>46086</v>
+        <v>46098</v>
       </c>
       <c r="B176" t="n">
-        <v>42.7125244140625</v>
+        <v>41.90911483764648</v>
       </c>
       <c r="C176" t="n">
-        <v>44.17521656583422</v>
+        <v>42.56655315831683</v>
       </c>
       <c r="D176" t="n">
-        <v>42.53582699299631</v>
+        <v>41.4773669245013</v>
       </c>
       <c r="E176" t="n">
-        <v>43.97888152103016</v>
+        <v>42.09555441402247</v>
       </c>
       <c r="F176" t="n">
-        <v>37085400</v>
+        <v>22436600</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
-        <v>46087</v>
+        <v>46099</v>
       </c>
       <c r="B177" t="n">
-        <v>42.14316177368164</v>
+        <v>41.48718643188477</v>
       </c>
       <c r="C177" t="n">
-        <v>42.79106487506458</v>
+        <v>42.2329374069265</v>
       </c>
       <c r="D177" t="n">
-        <v>41.86829492605856</v>
+        <v>41.47737559362956</v>
       </c>
       <c r="E177" t="n">
-        <v>42.66344651947674</v>
+        <v>41.70306230515991</v>
       </c>
       <c r="F177" t="n">
-        <v>26063600</v>
+        <v>23872800</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
-        <v>46090</v>
+        <v>46100</v>
       </c>
       <c r="B178" t="n">
-        <v>42.36894607543945</v>
+        <v>41.78155899047852</v>
       </c>
       <c r="C178" t="n">
-        <v>42.48674561881551</v>
+        <v>41.8011806646439</v>
       </c>
       <c r="D178" t="n">
-        <v>41.57379073189612</v>
+        <v>40.59424557252919</v>
       </c>
       <c r="E178" t="n">
-        <v>41.74067685106051</v>
+        <v>40.91805934374236</v>
       </c>
       <c r="F178" t="n">
-        <v>40970400</v>
+        <v>32908000</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
-        <v>46091</v>
+        <v>46101</v>
       </c>
       <c r="B179" t="n">
-        <v>42.99721145629883</v>
+        <v>41.10768127441406</v>
       </c>
       <c r="C179" t="n">
-        <v>43.38988155882488</v>
+        <v>41.82001776638332</v>
       </c>
       <c r="D179" t="n">
-        <v>42.0351738243676</v>
+        <v>40.76140868753353</v>
       </c>
       <c r="E179" t="n">
-        <v>42.78124627021117</v>
+        <v>41.66172118751106</v>
       </c>
       <c r="F179" t="n">
-        <v>50383100</v>
+        <v>37660900</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
-        <v>46092</v>
+        <v>46104</v>
       </c>
       <c r="B180" t="n">
-        <v>43.08556365966797</v>
+        <v>42.32458877563477</v>
       </c>
       <c r="C180" t="n">
-        <v>43.62548226232646</v>
+        <v>42.68075703713274</v>
       </c>
       <c r="D180" t="n">
-        <v>42.40821163939965</v>
+        <v>41.61225602672713</v>
       </c>
       <c r="E180" t="n">
-        <v>42.47692834820457</v>
+        <v>42.08714578402832</v>
       </c>
       <c r="F180" t="n">
-        <v>18482600</v>
+        <v>27535500</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
-        <v>46093</v>
+        <v>46105</v>
       </c>
       <c r="B181" t="n">
-        <v>41.90755844116211</v>
+        <v>42.08715057373047</v>
       </c>
       <c r="C181" t="n">
-        <v>42.42784692549765</v>
+        <v>42.35427680025408</v>
       </c>
       <c r="D181" t="n">
-        <v>41.52470712376984</v>
+        <v>41.51332302621559</v>
       </c>
       <c r="E181" t="n">
-        <v>42.30022857144026</v>
+        <v>42.04757547926281</v>
       </c>
       <c r="F181" t="n">
-        <v>27095200</v>
+        <v>18609000</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n">
-        <v>46094</v>
+        <v>46106</v>
       </c>
       <c r="B182" t="n">
-        <v>41.62287521362305</v>
+        <v>42.64118576049805</v>
       </c>
       <c r="C182" t="n">
-        <v>42.55546019020313</v>
+        <v>43.03692914735052</v>
       </c>
       <c r="D182" t="n">
-        <v>41.55415850471251</v>
+        <v>42.39384708723741</v>
       </c>
       <c r="E182" t="n">
-        <v>42.04499427966194</v>
+        <v>42.69065651442109</v>
       </c>
       <c r="F182" t="n">
-        <v>24896600</v>
+        <v>35148900</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n">
-        <v>46097</v>
+        <v>46107</v>
       </c>
       <c r="B183" t="n">
-        <v>42.21187591552734</v>
+        <v>41.49353408813477</v>
       </c>
       <c r="C183" t="n">
-        <v>42.67326273432889</v>
+        <v>42.38395481336692</v>
       </c>
       <c r="D183" t="n">
-        <v>42.06462368767757</v>
+        <v>41.49353408813477</v>
       </c>
       <c r="E183" t="n">
-        <v>42.45729379875716</v>
+        <v>42.23555010113203</v>
       </c>
       <c r="F183" t="n">
-        <v>17777300</v>
+        <v>18260900</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
-        <v>46098</v>
+        <v>46108</v>
       </c>
       <c r="B184" t="n">
-        <v>41.92719650268555</v>
+        <v>41.00874710083008</v>
       </c>
       <c r="C184" t="n">
-        <v>42.58491847476548</v>
+        <v>41.36491534484255</v>
       </c>
       <c r="D184" t="n">
-        <v>41.49526231213563</v>
+        <v>40.74162091782073</v>
       </c>
       <c r="E184" t="n">
-        <v>42.11371651831641</v>
+        <v>41.36491534484255</v>
       </c>
       <c r="F184" t="n">
-        <v>22436600</v>
+        <v>27910700</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n">
-        <v>46099</v>
+        <v>46111</v>
       </c>
       <c r="B185" t="n">
-        <v>41.50506973266602</v>
+        <v>41.15715026855469</v>
       </c>
       <c r="C185" t="n">
-        <v>42.25114216814269</v>
+        <v>41.61225625748603</v>
       </c>
       <c r="D185" t="n">
-        <v>41.49525466539009</v>
+        <v>40.79109011957994</v>
       </c>
       <c r="E185" t="n">
-        <v>41.72103866053236</v>
+        <v>41.55289362221108</v>
       </c>
       <c r="F185" t="n">
-        <v>23872800</v>
+        <v>18528100</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
-        <v>46100</v>
+        <v>46112</v>
       </c>
       <c r="B186" t="n">
-        <v>41.79957580566406</v>
+        <v>43.01714324951172</v>
       </c>
       <c r="C186" t="n">
-        <v>41.81920594098039</v>
+        <v>43.17543985550273</v>
       </c>
       <c r="D186" t="n">
-        <v>40.61175040092115</v>
+        <v>41.70130341985308</v>
       </c>
       <c r="E186" t="n">
-        <v>40.93570380533642</v>
+        <v>41.83981247833412</v>
       </c>
       <c r="F186" t="n">
-        <v>32908000</v>
+        <v>33419700</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n">
-        <v>46101</v>
+        <v>46113</v>
       </c>
       <c r="B187" t="n">
-        <v>41.12541580200195</v>
+        <v>43.38155746459961</v>
       </c>
       <c r="C187" t="n">
-        <v>41.83805960761132</v>
+        <v>43.82695029265173</v>
       </c>
       <c r="D187" t="n">
-        <v>40.77899382745093</v>
+        <v>43.05493202998284</v>
       </c>
       <c r="E187" t="n">
-        <v>41.67969473699994</v>
+        <v>43.39145348883009</v>
       </c>
       <c r="F187" t="n">
-        <v>37660900</v>
+        <v>26681100</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
-        <v>46104</v>
+        <v>46114</v>
       </c>
       <c r="B188" t="n">
-        <v>42.34284210205078</v>
+        <v>42.85697555541992</v>
       </c>
       <c r="C188" t="n">
-        <v>42.69916396824343</v>
+        <v>43.55971028853214</v>
       </c>
       <c r="D188" t="n">
-        <v>41.63020214538145</v>
+        <v>42.03546965877243</v>
       </c>
       <c r="E188" t="n">
-        <v>42.10529670839966</v>
+        <v>42.18393266927472</v>
       </c>
       <c r="F188" t="n">
-        <v>27535500</v>
+        <v>17811800</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
-        <v>46105</v>
+        <v>46118</v>
       </c>
       <c r="B189" t="n">
-        <v>42.10529708862305</v>
+        <v>43.04504013061523</v>
       </c>
       <c r="C189" t="n">
-        <v>42.3725384906808</v>
+        <v>43.29248229243014</v>
       </c>
       <c r="D189" t="n">
-        <v>41.53122212663617</v>
+        <v>42.75800631674968</v>
       </c>
       <c r="E189" t="n">
-        <v>42.06570493075168</v>
+        <v>42.90646934843797</v>
       </c>
       <c r="F189" t="n">
-        <v>18609000</v>
+        <v>11004600</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
-        <v>46106</v>
+        <v>46119</v>
       </c>
       <c r="B190" t="n">
-        <v>42.65957260131836</v>
+        <v>43.01534271240234</v>
       </c>
       <c r="C190" t="n">
-        <v>43.05548663236212</v>
+        <v>43.02524251283661</v>
       </c>
       <c r="D190" t="n">
-        <v>42.41212727584501</v>
+        <v>42.20373275750174</v>
       </c>
       <c r="E190" t="n">
-        <v>42.70906468698585</v>
+        <v>42.85697988646241</v>
       </c>
       <c r="F190" t="n">
-        <v>35148900</v>
+        <v>20302000</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n">
-        <v>46107</v>
+        <v>46120</v>
       </c>
       <c r="B191" t="n">
-        <v>41.51142501831055</v>
+        <v>44.51979064941406</v>
       </c>
       <c r="C191" t="n">
-        <v>42.40222966974644</v>
+        <v>45.26211709065173</v>
       </c>
       <c r="D191" t="n">
-        <v>41.51142501831055</v>
+        <v>44.24265665289894</v>
       </c>
       <c r="E191" t="n">
-        <v>42.25376096926849</v>
+        <v>45.23242524121584</v>
       </c>
       <c r="F191" t="n">
-        <v>18260900</v>
+        <v>35777600</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
-        <v>46108</v>
+        <v>46121</v>
       </c>
       <c r="B192" t="n">
-        <v>41.02643966674805</v>
+        <v>45.28191375732422</v>
       </c>
       <c r="C192" t="n">
-        <v>41.38276157383439</v>
+        <v>45.48976425857467</v>
       </c>
       <c r="D192" t="n">
-        <v>40.75919823643329</v>
+        <v>44.52969127751268</v>
       </c>
       <c r="E192" t="n">
-        <v>41.38276157383439</v>
+        <v>44.73754177876313</v>
       </c>
       <c r="F192" t="n">
-        <v>27910700</v>
+        <v>22162900</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
-        <v>46111</v>
+        <v>46122</v>
       </c>
       <c r="B193" t="n">
-        <v>41.17490005493164</v>
+        <v>45.59864044189453</v>
       </c>
       <c r="C193" t="n">
-        <v>41.63020231678347</v>
+        <v>45.90547007616472</v>
       </c>
       <c r="D193" t="n">
-        <v>40.8086820357107</v>
+        <v>45.30171060828953</v>
       </c>
       <c r="E193" t="n">
-        <v>41.5708140802682</v>
+        <v>45.3610980852776</v>
       </c>
       <c r="F193" t="n">
-        <v>18528100</v>
+        <v>29705900</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
-        <v>46112</v>
+        <v>46125</v>
       </c>
       <c r="B194" t="n">
-        <v>43.03569412231445</v>
+        <v>45.3610954284668</v>
       </c>
       <c r="C194" t="n">
-        <v>43.19405899272242</v>
+        <v>45.56894592224968</v>
       </c>
       <c r="D194" t="n">
-        <v>41.71928684499508</v>
+        <v>44.7771318204572</v>
       </c>
       <c r="E194" t="n">
-        <v>41.8578556346375</v>
+        <v>45.29180815487171</v>
       </c>
       <c r="F194" t="n">
-        <v>33419700</v>
+        <v>31011600</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
-        <v>46113</v>
+        <v>46126</v>
       </c>
       <c r="B195" t="n">
-        <v>43.40026473999023</v>
+        <v>46.05392837524414</v>
       </c>
       <c r="C195" t="n">
-        <v>43.84584963321424</v>
+        <v>46.36075797800192</v>
       </c>
       <c r="D195" t="n">
-        <v>43.07349845584403</v>
+        <v>45.38088547450708</v>
       </c>
       <c r="E195" t="n">
-        <v>43.4101650316482</v>
+        <v>45.5293522638954</v>
       </c>
       <c r="F195" t="n">
-        <v>26681100</v>
+        <v>23343300</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
-        <v>46114</v>
+        <v>46127</v>
       </c>
       <c r="B196" t="n">
-        <v>42.87545776367188</v>
+        <v>46.55871200561523</v>
       </c>
       <c r="C196" t="n">
-        <v>43.57849555339308</v>
+        <v>46.92492530018857</v>
       </c>
       <c r="D196" t="n">
-        <v>42.05359758996995</v>
+        <v>45.89556513502687</v>
       </c>
       <c r="E196" t="n">
-        <v>42.20212462562198</v>
+        <v>45.89556513502687</v>
       </c>
       <c r="F196" t="n">
-        <v>17811800</v>
+        <v>28907200</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
-        <v>46118</v>
+        <v>46128</v>
       </c>
       <c r="B197" t="n">
-        <v>43.06360244750977</v>
+        <v>46.49932479858398</v>
       </c>
       <c r="C197" t="n">
-        <v>43.31115131383248</v>
+        <v>46.98431303657651</v>
       </c>
       <c r="D197" t="n">
-        <v>42.77644485602439</v>
+        <v>46.04403218376147</v>
       </c>
       <c r="E197" t="n">
-        <v>42.92497190944046</v>
+        <v>46.78635857666798</v>
       </c>
       <c r="F197" t="n">
-        <v>11004600</v>
+        <v>22566300</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
-        <v>46119</v>
+        <v>46129</v>
       </c>
       <c r="B198" t="n">
-        <v>43.03389358520508</v>
+        <v>46.32117080688477</v>
       </c>
       <c r="C198" t="n">
-        <v>43.0437976550448</v>
+        <v>47.40991855771742</v>
       </c>
       <c r="D198" t="n">
-        <v>42.22193361395939</v>
+        <v>46.27168313086229</v>
       </c>
       <c r="E198" t="n">
-        <v>42.87546246343265</v>
+        <v>47.01400959820234</v>
       </c>
       <c r="F198" t="n">
-        <v>20302000</v>
+        <v>39165500</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
-        <v>46120</v>
+        <v>46132</v>
       </c>
       <c r="B199" t="n">
-        <v>44.53899002075195</v>
+        <v>45.89556884765625</v>
       </c>
       <c r="C199" t="n">
-        <v>45.28163659379599</v>
+        <v>46.54881597153135</v>
       </c>
       <c r="D199" t="n">
-        <v>44.26173650888351</v>
+        <v>45.75700184799602</v>
       </c>
       <c r="E199" t="n">
-        <v>45.25193193960888</v>
+        <v>46.32116964699416</v>
       </c>
       <c r="F199" t="n">
-        <v>35777600</v>
+        <v>19194500</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
-        <v>46121</v>
+        <v>46134</v>
       </c>
       <c r="B200" t="n">
-        <v>45.30143737792969</v>
+        <v>44.56927871704102</v>
       </c>
       <c r="C200" t="n">
-        <v>45.50937749540861</v>
+        <v>45.78669363833495</v>
       </c>
       <c r="D200" t="n">
-        <v>44.54889057202219</v>
+        <v>44.51979104232193</v>
       </c>
       <c r="E200" t="n">
-        <v>44.75683068950111</v>
+        <v>45.78669363833495</v>
       </c>
       <c r="F200" t="n">
-        <v>22162900</v>
+        <v>25440000</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
-        <v>46122</v>
+        <v>46135</v>
       </c>
       <c r="B201" t="n">
-        <v>45.61830139160156</v>
+        <v>43.72797393798828</v>
       </c>
       <c r="C201" t="n">
-        <v>45.92526332284266</v>
+        <v>44.6583549965339</v>
       </c>
       <c r="D201" t="n">
-        <v>45.32124352956264</v>
+        <v>43.66858646697449</v>
       </c>
       <c r="E201" t="n">
-        <v>45.38065661288868</v>
+        <v>44.4406084874846</v>
       </c>
       <c r="F201" t="n">
-        <v>29705900</v>
+        <v>20444200</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
-        <v>46125</v>
+        <v>46136</v>
       </c>
       <c r="B202" t="n">
-        <v>45.38066101074219</v>
+        <v>43.91603088378906</v>
       </c>
       <c r="C202" t="n">
-        <v>45.58860115659142</v>
+        <v>44.06449768121285</v>
       </c>
       <c r="D202" t="n">
-        <v>44.79644552195435</v>
+        <v>43.44094241796746</v>
       </c>
       <c r="E202" t="n">
-        <v>45.31134385149642</v>
+        <v>44.00511020710983</v>
       </c>
       <c r="F202" t="n">
-        <v>31011600</v>
+        <v>18234600</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
-        <v>46126</v>
+        <v>46139</v>
       </c>
       <c r="B203" t="n">
-        <v>46.07379150390625</v>
+        <v>43.53992080688477</v>
       </c>
       <c r="C203" t="n">
-        <v>46.38075344273376</v>
+        <v>44.10408858650873</v>
       </c>
       <c r="D203" t="n">
-        <v>45.40045831875256</v>
+        <v>43.53002100686754</v>
       </c>
       <c r="E203" t="n">
-        <v>45.54898914209071</v>
+        <v>44.04470111340768</v>
       </c>
       <c r="F203" t="n">
-        <v>23343300</v>
+        <v>13718400</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
-        <v>46127</v>
+        <v>46140</v>
       </c>
       <c r="B204" t="n">
-        <v>46.57879257202148</v>
+        <v>43.64879608154297</v>
       </c>
       <c r="C204" t="n">
-        <v>46.94516381276781</v>
+        <v>44.15358020888343</v>
       </c>
       <c r="D204" t="n">
-        <v>45.91535968912311</v>
+        <v>42.75800655935567</v>
       </c>
       <c r="E204" t="n">
-        <v>45.91535968912311</v>
+        <v>43.23309505965578</v>
       </c>
       <c r="F204" t="n">
-        <v>28907200</v>
+        <v>27131800</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
-        <v>46128</v>
+        <v>46141</v>
       </c>
       <c r="B205" t="n">
-        <v>46.51938247680664</v>
+        <v>42.43137741088867</v>
       </c>
       <c r="C205" t="n">
-        <v>47.00457991650396</v>
+        <v>43.55971297318277</v>
       </c>
       <c r="D205" t="n">
-        <v>46.06389346961058</v>
+        <v>42.32250226440986</v>
       </c>
       <c r="E205" t="n">
-        <v>46.80654006811126</v>
+        <v>43.40135015348653</v>
       </c>
       <c r="F205" t="n">
-        <v>22566300</v>
+        <v>18628100</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
-        <v>46129</v>
+        <v>46142</v>
       </c>
       <c r="B206" t="n">
-        <v>46.34114456176758</v>
+        <v>42.74810409545898</v>
       </c>
       <c r="C206" t="n">
-        <v>47.43036178218239</v>
+        <v>43.11432119269022</v>
       </c>
       <c r="D206" t="n">
-        <v>46.29163554658866</v>
+        <v>42.68872039641314</v>
       </c>
       <c r="E206" t="n">
-        <v>47.0342821061596</v>
+        <v>42.87677506950421</v>
       </c>
       <c r="F206" t="n">
-        <v>39165500</v>
+        <v>22735500</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
-        <v>46132</v>
+        <v>46146</v>
       </c>
       <c r="B207" t="n">
-        <v>45.91536331176758</v>
+        <v>41.98386383056641</v>
       </c>
       <c r="C207" t="n">
-        <v>46.56889217693217</v>
+        <v>42.82551993692074</v>
       </c>
       <c r="D207" t="n">
-        <v>45.77673654905023</v>
+        <v>41.83533450485321</v>
       </c>
       <c r="E207" t="n">
-        <v>46.34114766999711</v>
+        <v>42.68689458079251</v>
       </c>
       <c r="F207" t="n">
-        <v>19194500</v>
+        <v>25336300</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
-        <v>46134</v>
+        <v>46147</v>
       </c>
       <c r="B208" t="n">
-        <v>44.58849716186523</v>
+        <v>42.04327392578125</v>
       </c>
       <c r="C208" t="n">
-        <v>45.8064370371671</v>
+        <v>42.28092009930923</v>
       </c>
       <c r="D208" t="n">
-        <v>44.53898814787</v>
+        <v>41.70661071668364</v>
       </c>
       <c r="E208" t="n">
-        <v>45.8064370371671</v>
+        <v>42.08288225091221</v>
       </c>
       <c r="F208" t="n">
-        <v>25440000</v>
+        <v>29386700</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
-        <v>46135</v>
+        <v>46148</v>
       </c>
       <c r="B209" t="n">
-        <v>43.74683380126953</v>
+        <v>41.36994552612305</v>
       </c>
       <c r="C209" t="n">
-        <v>44.67761613291297</v>
+        <v>42.86512762151217</v>
       </c>
       <c r="D209" t="n">
-        <v>43.68742071645562</v>
+        <v>41.13230314123501</v>
       </c>
       <c r="E209" t="n">
-        <v>44.45977570985346</v>
+        <v>42.81561910609863</v>
       </c>
       <c r="F209" t="n">
-        <v>20444200</v>
+        <v>38718400</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
-        <v>46136</v>
+        <v>46149</v>
       </c>
       <c r="B210" t="n">
-        <v>43.93497085571289</v>
+        <v>40.38966751098633</v>
       </c>
       <c r="C210" t="n">
-        <v>44.08350168344447</v>
+        <v>41.45906588838612</v>
       </c>
       <c r="D210" t="n">
-        <v>43.45967749518604</v>
+        <v>40.1223169723219</v>
       </c>
       <c r="E210" t="n">
-        <v>44.02408859689267</v>
+        <v>41.37985301244365</v>
       </c>
       <c r="F210" t="n">
-        <v>18234600</v>
+        <v>36335300</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
-        <v>46139</v>
+        <v>46150</v>
       </c>
       <c r="B211" t="n">
-        <v>43.55870056152344</v>
+        <v>40.85505294799805</v>
       </c>
       <c r="C211" t="n">
-        <v>44.12311167949713</v>
+        <v>41.14220765572507</v>
       </c>
       <c r="D211" t="n">
-        <v>43.54879649149809</v>
+        <v>40.57780221074878</v>
       </c>
       <c r="E211" t="n">
-        <v>44.06369859123296</v>
+        <v>40.75603590676845</v>
       </c>
       <c r="F211" t="n">
-        <v>13718400</v>
+        <v>35920000</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n">
-        <v>46140</v>
+        <v>46153</v>
       </c>
       <c r="B212" t="n">
-        <v>43.66761779785156</v>
+        <v>39.93418502807617</v>
       </c>
       <c r="C212" t="n">
-        <v>44.17261959221826</v>
+        <v>40.70652854803431</v>
       </c>
       <c r="D212" t="n">
-        <v>42.77644415996848</v>
+        <v>39.71634299844363</v>
       </c>
       <c r="E212" t="n">
-        <v>43.25173752229863</v>
+        <v>40.54809901119012</v>
       </c>
       <c r="F212" t="n">
-        <v>27131800</v>
+        <v>41215600</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n">
-        <v>46141</v>
+        <v>46154</v>
       </c>
       <c r="B213" t="n">
-        <v>42.44967651367188</v>
+        <v>39.47869110107422</v>
       </c>
       <c r="C213" t="n">
-        <v>43.57849868586856</v>
+        <v>39.93417925879786</v>
       </c>
       <c r="D213" t="n">
-        <v>42.34075441332031</v>
+        <v>39.37967407132335</v>
       </c>
       <c r="E213" t="n">
-        <v>43.42006757007421</v>
+        <v>39.89457093599449</v>
       </c>
       <c r="F213" t="n">
-        <v>18628100</v>
+        <v>43381700</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
-        <v>46142</v>
+        <v>46155</v>
       </c>
       <c r="B214" t="n">
-        <v>42.76653671264648</v>
+        <v>39.24105072021484</v>
       </c>
       <c r="C214" t="n">
-        <v>43.13291171956059</v>
+        <v>40.17182369002172</v>
       </c>
       <c r="D214" t="n">
-        <v>42.70712740785707</v>
+        <v>38.98360038611953</v>
       </c>
       <c r="E214" t="n">
-        <v>42.89526316851619</v>
+        <v>39.53810560187596</v>
       </c>
       <c r="F214" t="n">
-        <v>22735500</v>
+        <v>48564700</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
-        <v>46146</v>
+        <v>46156</v>
       </c>
       <c r="B215" t="n">
-        <v>42.00196838378906</v>
+        <v>40.00349426269531</v>
       </c>
       <c r="C215" t="n">
-        <v>42.84398743453161</v>
+        <v>40.25104062873363</v>
       </c>
       <c r="D215" t="n">
-        <v>41.85337500829966</v>
+        <v>39.59751837348278</v>
       </c>
       <c r="E215" t="n">
-        <v>42.70530229948098</v>
+        <v>39.75594789665699</v>
       </c>
       <c r="F215" t="n">
-        <v>25336300</v>
+        <v>34925200</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
-        <v>46147</v>
+        <v>46157</v>
       </c>
       <c r="B216" t="n">
-        <v>42.06140518188477</v>
+        <v>39.31035995483398</v>
       </c>
       <c r="C216" t="n">
-        <v>42.29915384085768</v>
+        <v>39.65692332352255</v>
       </c>
       <c r="D216" t="n">
-        <v>41.72459678602374</v>
+        <v>39.19153876803468</v>
       </c>
       <c r="E216" t="n">
-        <v>42.10103058819471</v>
+        <v>39.38957282028105</v>
       </c>
       <c r="F216" t="n">
-        <v>29386700</v>
+        <v>46869600</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
-        <v>46148</v>
+        <v>46160</v>
       </c>
       <c r="B217" t="n">
-        <v>41.38778686523438</v>
+        <v>39.23114776611328</v>
       </c>
       <c r="C217" t="n">
-        <v>42.88361377778382</v>
+        <v>39.45888997385853</v>
       </c>
       <c r="D217" t="n">
-        <v>41.15004199390788</v>
+        <v>38.9142887138366</v>
       </c>
       <c r="E217" t="n">
-        <v>42.83408391116468</v>
+        <v>39.28065628479567</v>
       </c>
       <c r="F217" t="n">
-        <v>38718400</v>
+        <v>22993100</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
-        <v>46149</v>
+        <v>46161</v>
       </c>
       <c r="B218" t="n">
-        <v>40.40708160400391</v>
+        <v>38.39939117431641</v>
       </c>
       <c r="C218" t="n">
-        <v>41.47694105484066</v>
+        <v>39.03310926838592</v>
       </c>
       <c r="D218" t="n">
-        <v>40.1396157965731</v>
+        <v>38.32017830118661</v>
       </c>
       <c r="E218" t="n">
-        <v>41.3976940260944</v>
+        <v>38.66674170348782</v>
       </c>
       <c r="F218" t="n">
-        <v>36335300</v>
+        <v>41150400</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
-        <v>46150</v>
+        <v>46162</v>
       </c>
       <c r="B219" t="n">
-        <v>40.8726692199707</v>
+        <v>39.28065490722656</v>
       </c>
       <c r="C219" t="n">
-        <v>41.15994774580748</v>
+        <v>39.58761375590489</v>
       </c>
       <c r="D219" t="n">
-        <v>40.59529893510028</v>
+        <v>38.71624950407376</v>
       </c>
       <c r="E219" t="n">
-        <v>40.77360948362747</v>
+        <v>38.83507447745372</v>
       </c>
       <c r="F219" t="n">
-        <v>35920000</v>
+        <v>38261500</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
-        <v>46153</v>
+        <v>46163</v>
       </c>
       <c r="B220" t="n">
-        <v>39.95140075683594</v>
+        <v>39.72623825073242</v>
       </c>
       <c r="C220" t="n">
-        <v>40.72407723605041</v>
+        <v>40.05300125453793</v>
       </c>
       <c r="D220" t="n">
-        <v>39.73346481495022</v>
+        <v>38.86477798737062</v>
       </c>
       <c r="E220" t="n">
-        <v>40.56557939982984</v>
+        <v>39.04301166630859</v>
       </c>
       <c r="F220" t="n">
-        <v>41215600</v>
+        <v>40949800</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n">
-        <v>46154</v>
+        <v>46164</v>
       </c>
       <c r="B221" t="n">
-        <v>39.49571990966797</v>
+        <v>39.04301071166992</v>
       </c>
       <c r="C221" t="n">
-        <v>39.9514045384609</v>
+        <v>39.64702441138463</v>
       </c>
       <c r="D221" t="n">
-        <v>39.39666016973599</v>
+        <v>38.92418952103577</v>
       </c>
       <c r="E221" t="n">
-        <v>39.91177913093337</v>
+        <v>39.61731628078293</v>
       </c>
       <c r="F221" t="n">
-        <v>43381700</v>
+        <v>21539700</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n">
-        <v>46155</v>
+        <v>46167</v>
       </c>
       <c r="B222" t="n">
-        <v>39.25797271728516</v>
+        <v>39.92427825927734</v>
       </c>
       <c r="C222" t="n">
-        <v>40.18914706618814</v>
+        <v>40.09261175508455</v>
       </c>
       <c r="D222" t="n">
-        <v>39.00041136236549</v>
+        <v>39.46879384492958</v>
       </c>
       <c r="E222" t="n">
-        <v>39.55515569851916</v>
+        <v>39.46879384492958</v>
       </c>
       <c r="F222" t="n">
-        <v>48564700</v>
+        <v>11436200</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="n">
-        <v>46156</v>
+        <v>46168</v>
       </c>
       <c r="B223" t="n">
-        <v>40.02074432373047</v>
+        <v>39.66683197021484</v>
       </c>
       <c r="C223" t="n">
-        <v>40.26839743519195</v>
+        <v>39.96388686087212</v>
       </c>
       <c r="D223" t="n">
-        <v>39.6145933720891</v>
+        <v>39.26085607162306</v>
       </c>
       <c r="E223" t="n">
-        <v>39.77309121226898</v>
+        <v>39.82526149704925</v>
       </c>
       <c r="F223" t="n">
-        <v>34925200</v>
+        <v>23046600</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n">
-        <v>46157</v>
+        <v>46169</v>
       </c>
       <c r="B224" t="n">
-        <v>39.32731628417969</v>
+        <v>39.92427825927734</v>
       </c>
       <c r="C224" t="n">
-        <v>39.6740291412633</v>
+        <v>40.41937099937479</v>
       </c>
       <c r="D224" t="n">
-        <v>39.20844384444912</v>
+        <v>39.89457390359401</v>
       </c>
       <c r="E224" t="n">
-        <v>39.40656331770449</v>
+        <v>40.2015289850094</v>
       </c>
       <c r="F224" t="n">
-        <v>46869600</v>
+        <v>21601400</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="n">
-        <v>46160</v>
+        <v>46170</v>
       </c>
       <c r="B225" t="n">
-        <v>39.24806213378906</v>
+        <v>39.60741806030273</v>
       </c>
       <c r="C225" t="n">
-        <v>39.47590253176469</v>
+        <v>40.05300226893269</v>
       </c>
       <c r="D225" t="n">
-        <v>38.93106646887633</v>
+        <v>39.33016734260309</v>
       </c>
       <c r="E225" t="n">
-        <v>39.29759199789048</v>
+        <v>39.92427710260453</v>
       </c>
       <c r="F225" t="n">
-        <v>22993100</v>
+        <v>20196600</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="B226" t="n">
-        <v>38.41594696044922</v>
+        <v>39.64702224731445</v>
       </c>
       <c r="C226" t="n">
-        <v>39.04993828023698</v>
+        <v>39.76584343146293</v>
       </c>
       <c r="D226" t="n">
-        <v>38.33669993491892</v>
+        <v>39.15192957322888</v>
       </c>
       <c r="E226" t="n">
-        <v>38.68341275702587</v>
+        <v>39.47868877395154</v>
       </c>
       <c r="F226" t="n">
-        <v>41150400</v>
+        <v>80334400</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="n">
-        <v>46162</v>
+        <v>46174</v>
       </c>
       <c r="B227" t="n">
-        <v>39.29759216308594</v>
+        <v>38.99140167236328</v>
       </c>
       <c r="C227" t="n">
-        <v>39.60468336802387</v>
+        <v>39.68484706096815</v>
       </c>
       <c r="D227" t="n">
-        <v>38.73294339640612</v>
+        <v>38.88243119685737</v>
       </c>
       <c r="E227" t="n">
-        <v>38.85181960541292</v>
+        <v>39.67493859284578</v>
       </c>
       <c r="F227" t="n">
-        <v>38261500</v>
+        <v>32832400</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n">
-        <v>46163</v>
+        <v>46175</v>
       </c>
       <c r="B228" t="n">
-        <v>39.74337005615234</v>
+        <v>39.18953323364258</v>
       </c>
       <c r="C228" t="n">
-        <v>40.07027397539425</v>
+        <v>39.61550670849539</v>
       </c>
       <c r="D228" t="n">
-        <v>38.88153829097565</v>
+        <v>39.10037590683679</v>
       </c>
       <c r="E228" t="n">
-        <v>39.05984883258277</v>
+        <v>39.25887740127223</v>
       </c>
       <c r="F228" t="n">
-        <v>40949800</v>
+        <v>23121000</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="n">
-        <v>46164</v>
+        <v>46176</v>
       </c>
       <c r="B229" t="n">
-        <v>39.05985260009766</v>
+        <v>38.35739898681641</v>
       </c>
       <c r="C229" t="n">
-        <v>39.66412685173072</v>
+        <v>38.93196548019473</v>
       </c>
       <c r="D229" t="n">
-        <v>38.94098015385593</v>
+        <v>38.27814635105461</v>
       </c>
       <c r="E229" t="n">
-        <v>39.63440590600509</v>
+        <v>38.86262131338999</v>
       </c>
       <c r="F229" t="n">
-        <v>21539700</v>
+        <v>40844400</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n">
-        <v>46167</v>
+        <v>46178</v>
       </c>
       <c r="B230" t="n">
-        <v>39.94149398803711</v>
+        <v>38.46636962890625</v>
       </c>
       <c r="C230" t="n">
-        <v>40.1099000708498</v>
+        <v>38.8031819953511</v>
       </c>
       <c r="D230" t="n">
-        <v>39.48581316447486</v>
+        <v>38.20880234060013</v>
       </c>
       <c r="E230" t="n">
-        <v>39.48581316447486</v>
+        <v>38.38711699282015</v>
       </c>
       <c r="F230" t="n">
-        <v>11436200</v>
+        <v>34727700</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="n">
-        <v>46168</v>
+        <v>46181</v>
       </c>
       <c r="B231" t="n">
-        <v>39.68393707275391</v>
+        <v>38.15927124023438</v>
       </c>
       <c r="C231" t="n">
-        <v>39.98112005920589</v>
+        <v>38.71402835457415</v>
       </c>
       <c r="D231" t="n">
-        <v>39.27778610952931</v>
+        <v>38.07011391434001</v>
       </c>
       <c r="E231" t="n">
-        <v>39.84243491745407</v>
+        <v>38.3573990509967</v>
       </c>
       <c r="F231" t="n">
-        <v>23046600</v>
+        <v>23153100</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n">
-        <v>46169</v>
+        <v>46182</v>
       </c>
       <c r="B232" t="n">
-        <v>39.94149398803711</v>
+        <v>38.85271453857422</v>
       </c>
       <c r="C232" t="n">
-        <v>40.43680021683607</v>
+        <v>38.97158970686441</v>
       </c>
       <c r="D232" t="n">
-        <v>39.91177682355289</v>
+        <v>38.40692793376917</v>
       </c>
       <c r="E232" t="n">
-        <v>40.2188642669208</v>
+        <v>38.55552094938854</v>
       </c>
       <c r="F232" t="n">
-        <v>21601400</v>
+        <v>28212000</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n">
-        <v>46170</v>
+        <v>46183</v>
       </c>
       <c r="B233" t="n">
-        <v>39.62449645996094</v>
+        <v>38.99140167236328</v>
       </c>
       <c r="C233" t="n">
-        <v>40.07027280091279</v>
+        <v>39.21924731252412</v>
       </c>
       <c r="D233" t="n">
-        <v>39.34712619398488</v>
+        <v>38.2880515946094</v>
       </c>
       <c r="E233" t="n">
-        <v>39.94149212932971</v>
+        <v>38.66449024584556</v>
       </c>
       <c r="F233" t="n">
-        <v>20196600</v>
+        <v>41470600</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="n">
-        <v>46171</v>
+        <v>46184</v>
       </c>
       <c r="B234" t="n">
-        <v>39.66412353515625</v>
+        <v>40.12073135375977</v>
       </c>
       <c r="C234" t="n">
-        <v>39.78299597145828</v>
+        <v>40.23960653669524</v>
       </c>
       <c r="D234" t="n">
-        <v>39.16881730853009</v>
+        <v>38.8527193251842</v>
       </c>
       <c r="E234" t="n">
-        <v>39.49571745308231</v>
+        <v>38.87253248550244</v>
       </c>
       <c r="F234" t="n">
-        <v>80334400</v>
+        <v>57558800</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="n">
-        <v>46174</v>
+        <v>46185</v>
       </c>
       <c r="B235" t="n">
-        <v>39.00822067260742</v>
+        <v>40.21978759765625</v>
       </c>
       <c r="C235" t="n">
-        <v>39.70196517993232</v>
+        <v>40.73491835499532</v>
       </c>
       <c r="D235" t="n">
-        <v>38.89920319252165</v>
+        <v>39.73437846601114</v>
       </c>
       <c r="E235" t="n">
-        <v>39.6920524377772</v>
+        <v>39.84334894261774</v>
       </c>
       <c r="F235" t="n">
-        <v>32832400</v>
+        <v>30651000</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="n">
-        <v>46175</v>
+        <v>46188</v>
       </c>
       <c r="B236" t="n">
-        <v>39.2064323425293</v>
+        <v>40.02166748046875</v>
       </c>
       <c r="C236" t="n">
-        <v>39.63258950347225</v>
+        <v>41.10146010455043</v>
       </c>
       <c r="D236" t="n">
-        <v>39.11723656975977</v>
+        <v>39.94241484286059</v>
       </c>
       <c r="E236" t="n">
-        <v>39.27580641239413</v>
+        <v>40.8934238203159</v>
       </c>
       <c r="F236" t="n">
-        <v>23121000</v>
+        <v>25132500</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="n">
-        <v>46176</v>
+        <v>46189</v>
       </c>
       <c r="B237" t="n">
-        <v>38.37393951416016</v>
+        <v>40.07119750976562</v>
       </c>
       <c r="C237" t="n">
-        <v>38.94875377284701</v>
+        <v>40.24951216105051</v>
       </c>
       <c r="D237" t="n">
-        <v>38.29465270297398</v>
+        <v>39.75419452503109</v>
       </c>
       <c r="E237" t="n">
-        <v>38.87937970336073</v>
+        <v>39.90278754845271</v>
       </c>
       <c r="F237" t="n">
-        <v>40844400</v>
+        <v>20052700</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="n">
-        <v>46178</v>
+        <v>46190</v>
       </c>
       <c r="B238" t="n">
-        <v>38.48295593261719</v>
+        <v>40.41791915893555</v>
       </c>
       <c r="C238" t="n">
-        <v>38.81991352909693</v>
+        <v>41.24014826522593</v>
       </c>
       <c r="D238" t="n">
-        <v>38.22527758394038</v>
+        <v>40.24951297319823</v>
       </c>
       <c r="E238" t="n">
-        <v>38.40366912360798</v>
+        <v>40.5665159643292</v>
       </c>
       <c r="F238" t="n">
-        <v>34727700</v>
+        <v>28205700</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="n">
-        <v>46181</v>
+        <v>46191</v>
       </c>
       <c r="B239" t="n">
-        <v>38.17572784423828</v>
+        <v>40.11082458496094</v>
       </c>
       <c r="C239" t="n">
-        <v>38.73072420366456</v>
+        <v>40.99248938908703</v>
       </c>
       <c r="D239" t="n">
-        <v>38.08653206826983</v>
+        <v>40.08110295653649</v>
       </c>
       <c r="E239" t="n">
-        <v>38.37394109979076</v>
+        <v>40.53679428332489</v>
       </c>
       <c r="F239" t="n">
-        <v>23153100</v>
+        <v>20051100</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="n">
-        <v>46182</v>
+        <v>46192</v>
       </c>
       <c r="B240" t="n">
-        <v>38.86947250366211</v>
+        <v>39.85281372070312</v>
       </c>
       <c r="C240" t="n">
-        <v>38.98839894522738</v>
+        <v>40.35259820513199</v>
       </c>
       <c r="D240" t="n">
-        <v>38.42349362203809</v>
+        <v>39.74286052404029</v>
       </c>
       <c r="E240" t="n">
-        <v>38.57215072884382</v>
+        <v>40.34260419318674</v>
       </c>
       <c r="F240" t="n">
-        <v>28212000</v>
+        <v>48413400</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="n">
-        <v>46183</v>
+        <v>46195</v>
       </c>
       <c r="B241" t="n">
-        <v>39.00822067260742</v>
+        <v>40.9223518371582</v>
       </c>
       <c r="C241" t="n">
-        <v>39.23616459433068</v>
+        <v>41.00231918419912</v>
       </c>
       <c r="D241" t="n">
-        <v>38.30456720373083</v>
+        <v>40.08271375849343</v>
       </c>
       <c r="E241" t="n">
-        <v>38.68116823235008</v>
+        <v>40.14268926877413</v>
       </c>
       <c r="F241" t="n">
-        <v>41470600</v>
+        <v>25404800</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="n">
-        <v>46184</v>
+        <v>46196</v>
       </c>
       <c r="B242" t="n">
-        <v>40.13803100585938</v>
+        <v>41.03230285644531</v>
       </c>
       <c r="C242" t="n">
-        <v>40.25695744656705</v>
+        <v>41.36216242591377</v>
       </c>
       <c r="D242" t="n">
-        <v>38.86947222336851</v>
+        <v>40.37258753056117</v>
       </c>
       <c r="E242" t="n">
-        <v>38.88929392692035</v>
+        <v>40.50253255608384</v>
       </c>
       <c r="F242" t="n">
-        <v>57558800</v>
+        <v>21074900</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="n">
-        <v>46185</v>
+        <v>46197</v>
       </c>
       <c r="B243" t="n">
-        <v>40.23713302612305</v>
+        <v>40.95233917236328</v>
       </c>
       <c r="C243" t="n">
-        <v>40.75248594186314</v>
+        <v>41.46211763510372</v>
       </c>
       <c r="D243" t="n">
-        <v>39.75151455400468</v>
+        <v>40.79240830041994</v>
       </c>
       <c r="E243" t="n">
-        <v>39.86053202587704</v>
+        <v>40.79240830041994</v>
       </c>
       <c r="F243" t="n">
-        <v>30651000</v>
+        <v>22041600</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="n">
-        <v>46188</v>
+        <v>46198</v>
       </c>
       <c r="B244" t="n">
-        <v>40.03892517089844</v>
+        <v>41.68202590942383</v>
       </c>
       <c r="C244" t="n">
-        <v>41.11918341093287</v>
+        <v>42.09184902573129</v>
       </c>
       <c r="D244" t="n">
-        <v>39.95963835886499</v>
+        <v>41.20223327177506</v>
       </c>
       <c r="E244" t="n">
-        <v>40.9110574196467</v>
+        <v>41.28219680485672</v>
       </c>
       <c r="F244" t="n">
-        <v>25132500</v>
+        <v>20778400</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="n">
-        <v>46189</v>
+        <v>46199</v>
       </c>
       <c r="B245" t="n">
-        <v>40.08847808837891</v>
+        <v>42.22179412841797</v>
       </c>
       <c r="C245" t="n">
-        <v>40.26686963729952</v>
+        <v>42.52166405082638</v>
       </c>
       <c r="D245" t="n">
-        <v>39.77133839709855</v>
+        <v>41.38215605784266</v>
       </c>
       <c r="E245" t="n">
-        <v>39.91999550079684</v>
+        <v>41.49210543938516</v>
       </c>
       <c r="F245" t="n">
-        <v>20052700</v>
+        <v>23047700</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="n">
-        <v>46190</v>
+        <v>46202</v>
       </c>
       <c r="B246" t="n">
-        <v>40.43534851074219</v>
+        <v>42.39171981811523</v>
       </c>
       <c r="C246" t="n">
-        <v>41.25793218551748</v>
+        <v>42.5916343745039</v>
       </c>
       <c r="D246" t="n">
-        <v>40.26686970348653</v>
+        <v>42.02188036728067</v>
       </c>
       <c r="E246" t="n">
-        <v>40.58400939528817</v>
+        <v>42.22179492366933</v>
       </c>
       <c r="F246" t="n">
-        <v>28205700</v>
+        <v>21151300</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="n">
-        <v>46191</v>
+        <v>46203</v>
       </c>
       <c r="B247" t="n">
-        <v>40.12812042236328</v>
+        <v>42.16181945800781</v>
       </c>
       <c r="C247" t="n">
-        <v>41.01016540144847</v>
+        <v>42.50167306031674</v>
       </c>
       <c r="D247" t="n">
-        <v>40.09838597793572</v>
+        <v>41.62205129909604</v>
       </c>
       <c r="E247" t="n">
-        <v>40.55427379939048</v>
+        <v>42.07185809818918</v>
       </c>
       <c r="F247" t="n">
-        <v>20051100</v>
+        <v>40172400</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="n">
-        <v>46192</v>
+        <v>46204</v>
       </c>
       <c r="B248" t="n">
-        <v>39.86999893188477</v>
+        <v>42.43999862670898</v>
       </c>
       <c r="C248" t="n">
-        <v>40.36999893188477</v>
+        <v>42.79999923706055</v>
       </c>
       <c r="D248" t="n">
-        <v>39.7599983215332</v>
+        <v>41.47000122070312</v>
       </c>
       <c r="E248" t="n">
-        <v>40.36000061035156</v>
+        <v>41.70000076293945</v>
       </c>
       <c r="F248" t="n">
-        <v>48413400</v>
+        <v>26405300</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="n">
-        <v>46195</v>
+        <v>46205</v>
       </c>
       <c r="B249" t="n">
-        <v>40.93999862670898</v>
+        <v>42.47000122070312</v>
       </c>
       <c r="C249" t="n">
-        <v>41.02000045776367</v>
+        <v>43.15999984741211</v>
       </c>
       <c r="D249" t="n">
-        <v>40.09999847412109</v>
+        <v>42.31000137329102</v>
       </c>
       <c r="E249" t="n">
-        <v>40.15999984741211</v>
+        <v>42.70999908447266</v>
       </c>
       <c r="F249" t="n">
-        <v>25404800</v>
+        <v>15005100</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="n">
-        <v>46196</v>
+        <v>46206</v>
       </c>
       <c r="B250" t="n">
-        <v>41.04999923706055</v>
+        <v>42.7400016784668</v>
       </c>
       <c r="C250" t="n">
-        <v>41.38000106811523</v>
+        <v>42.88999938964844</v>
       </c>
       <c r="D250" t="n">
-        <v>40.38999938964844</v>
+        <v>42.52999877929688</v>
       </c>
       <c r="E250" t="n">
-        <v>40.52000045776367</v>
+        <v>42.79000091552734</v>
       </c>
       <c r="F250" t="n">
-        <v>21074900</v>
+        <v>9878400</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="n">
-        <v>46197</v>
+        <v>46209</v>
       </c>
       <c r="B251" t="n">
-        <v>40.97000122070312</v>
+        <v>42.56000137329102</v>
       </c>
       <c r="C251" t="n">
-        <v>41.47999954223633</v>
+        <v>42.66999816894531</v>
       </c>
       <c r="D251" t="n">
-        <v>40.81000137329102</v>
+        <v>42.04999923706055</v>
       </c>
       <c r="E251" t="n">
-        <v>40.81000137329102</v>
+        <v>42.4900016784668</v>
       </c>
       <c r="F251" t="n">
-        <v>22041600</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" s="2" t="n">
-        <v>46198</v>
-      </c>
-      <c r="B252" t="n">
-        <v>41.7400016784668</v>
-      </c>
-      <c r="C252" t="n">
-        <v>42.11000061035156</v>
-      </c>
-      <c r="D252" t="n">
-        <v>41.22000122070312</v>
-      </c>
-      <c r="E252" t="n">
-        <v>41.29999923706055</v>
-      </c>
-      <c r="F252" t="n">
-        <v>15950900</v>
+        <v>19155100</v>
       </c>
     </row>
   </sheetData>
